--- a/data/Krónan_Master_Skrá.xlsx
+++ b/data/Krónan_Master_Skrá.xlsx
@@ -20,10 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -94,7 +93,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -116,16 +115,61 @@
         <color rgb="00BDC3C7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BDC3C7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BDC3C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDC3C7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BDC3C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BDC3C7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BDC3C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDC3C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BDC3C7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -140,10 +184,10 @@
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,7 +202,7 @@
     <xf numFmtId="3" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -179,7 +223,7 @@
     <xf numFmtId="3" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -194,7 +238,25 @@
     <xf numFmtId="3" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -606,7 +668,7 @@
       </c>
     </row>
     <row r="2" ht="17" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -625,12 +687,12 @@
       <c r="E2" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="27" t="n">
         <v>0.1644306780604176</v>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -649,12 +711,12 @@
       <c r="E3" s="12" t="n">
         <v>480</v>
       </c>
-      <c r="F3" s="13" t="n">
+      <c r="F3" s="29" t="n">
         <v>0.1546576645076558</v>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -673,12 +735,12 @@
       <c r="E4" s="6" t="n">
         <v>419</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="27" t="n">
         <v>0.1498387342328305</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -697,12 +759,12 @@
       <c r="E5" s="12" t="n">
         <v>322</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="29" t="n">
         <v>0.1016817909203893</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -721,12 +783,12 @@
       <c r="E6" s="6" t="n">
         <v>327</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="27" t="n">
         <v>0.08668660355875986</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -745,12 +807,12 @@
       <c r="E7" s="12" t="n">
         <v>345</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="29" t="n">
         <v>0.08629562909175065</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -769,12 +831,12 @@
       <c r="E8" s="6" t="n">
         <v>322</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="27" t="n">
         <v>0.08539074470938997</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -793,12 +855,12 @@
       <c r="E9" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="29" t="n">
         <v>0.02251612927766518</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -817,12 +879,12 @@
       <c r="E10" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="27" t="n">
         <v>0.02243930628162347</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -841,12 +903,12 @@
       <c r="E11" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="29" t="n">
         <v>0.02242239692436817</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -865,12 +927,12 @@
       <c r="E12" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="27" t="n">
         <v>0.02224079646695759</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -889,12 +951,12 @@
       <c r="E13" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="29" t="n">
         <v>0.0205676457038032</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -913,12 +975,12 @@
       <c r="E14" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="27" t="n">
         <v>0.01865081229872824</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -937,12 +999,12 @@
       <c r="E15" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="29" t="n">
         <v>0.01685023423502563</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -961,12 +1023,12 @@
       <c r="E16" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="27" t="n">
         <v>0.01462453853145174</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -985,12 +1047,12 @@
       <c r="E17" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="29" t="n">
         <v>0.00677795959790408</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1009,12 +1071,12 @@
       <c r="E18" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="27" t="n">
         <v>0.00304830283698442</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1033,7 +1095,7 @@
       <c r="E19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="29" t="n">
         <v>0.0008800327642946427</v>
       </c>
     </row>
@@ -1109,8 +1171,8 @@
       <c r="D3" s="12" t="n">
         <v>550</v>
       </c>
-      <c r="E3" s="13" t="n">
-        <v>0.1644306780604176</v>
+      <c r="E3" s="29" t="n">
+        <v>0.1644306780604177</v>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
@@ -1130,7 +1192,7 @@
       <c r="D4" s="6" t="n">
         <v>480</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="27" t="n">
         <v>0.1546576645076558</v>
       </c>
     </row>
@@ -1151,7 +1213,7 @@
       <c r="D5" s="12" t="n">
         <v>419</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="29" t="n">
         <v>0.1498387342328305</v>
       </c>
     </row>
@@ -1172,7 +1234,7 @@
       <c r="D6" s="6" t="n">
         <v>322</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="27" t="n">
         <v>0.1016817909203893</v>
       </c>
     </row>
@@ -1193,8 +1255,8 @@
       <c r="D7" s="12" t="n">
         <v>327</v>
       </c>
-      <c r="E7" s="13" t="n">
-        <v>0.08668660355875986</v>
+      <c r="E7" s="29" t="n">
+        <v>0.08668660355875987</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -1214,8 +1276,8 @@
       <c r="D8" s="6" t="n">
         <v>345</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>0.08629562909175065</v>
+      <c r="E8" s="27" t="n">
+        <v>0.08629562909175066</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -1235,8 +1297,8 @@
       <c r="D9" s="12" t="n">
         <v>322</v>
       </c>
-      <c r="E9" s="13" t="n">
-        <v>0.08539074470938997</v>
+      <c r="E9" s="29" t="n">
+        <v>0.08539074470938998</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -1256,7 +1318,7 @@
       <c r="D10" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="27" t="n">
         <v>0.02251612927766518</v>
       </c>
     </row>
@@ -1277,8 +1339,8 @@
       <c r="D11" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="E11" s="13" t="n">
-        <v>0.02243930628162347</v>
+      <c r="E11" s="29" t="n">
+        <v>0.02243930628162348</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -1298,7 +1360,7 @@
       <c r="D12" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="27" t="n">
         <v>0.02242239692436817</v>
       </c>
     </row>
@@ -1319,7 +1381,7 @@
       <c r="D13" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="29" t="n">
         <v>0.02224079646695759</v>
       </c>
     </row>
@@ -1340,7 +1402,7 @@
       <c r="D14" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="27" t="n">
         <v>0.0205676457038032</v>
       </c>
     </row>
@@ -1361,7 +1423,7 @@
       <c r="D15" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="29" t="n">
         <v>0.01865081229872824</v>
       </c>
     </row>
@@ -1382,8 +1444,8 @@
       <c r="D16" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>0.01685023423502563</v>
+      <c r="E16" s="27" t="n">
+        <v>0.01685023423502564</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1403,7 +1465,7 @@
       <c r="D17" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="29" t="n">
         <v>0.01462453853145174</v>
       </c>
     </row>
@@ -1424,7 +1486,7 @@
       <c r="D18" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="27" t="n">
         <v>0.00677795959790408</v>
       </c>
     </row>
@@ -1445,8 +1507,8 @@
       <c r="D19" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0.00304830283698442</v>
+      <c r="E19" s="29" t="n">
+        <v>0.003048302836984421</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -1466,8 +1528,8 @@
       <c r="D20" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="7" t="n">
-        <v>0.0008800327642946427</v>
+      <c r="E20" s="27" t="n">
+        <v>0.0008800327642946428</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1482,12 +1544,12 @@
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>5804442.979</v>
+        <v>5804442.978999999</v>
       </c>
       <c r="D21" s="19" t="n">
         <v>3331</v>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -1551,7 +1613,7 @@
       </c>
     </row>
     <row r="2" ht="17" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1570,12 +1632,12 @@
       <c r="E2" s="6" t="n">
         <v>136</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="27" t="n">
         <v>0.08415142396242654</v>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -1594,12 +1656,12 @@
       <c r="E3" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="F3" s="13" t="n">
+      <c r="F3" s="29" t="n">
         <v>0.07362952773577183</v>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1618,12 +1680,12 @@
       <c r="E4" s="6" t="n">
         <v>170</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="27" t="n">
         <v>0.05595070715055255</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -1642,12 +1704,12 @@
       <c r="E5" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="29" t="n">
         <v>0.05048134204149805</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1666,12 +1728,12 @@
       <c r="E6" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="27" t="n">
         <v>0.04680974475315454</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -1690,12 +1752,12 @@
       <c r="E7" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="29" t="n">
         <v>0.04622520202139142</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1714,12 +1776,12 @@
       <c r="E8" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="27" t="n">
         <v>0.04549643569171832</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -1738,12 +1800,12 @@
       <c r="E9" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="29" t="n">
         <v>0.0431615208380664</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1762,12 +1824,12 @@
       <c r="E10" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="27" t="n">
         <v>0.0377459531178134</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -1786,12 +1848,12 @@
       <c r="E11" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="29" t="n">
         <v>0.0326909828562989</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1810,12 +1872,12 @@
       <c r="E12" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="27" t="n">
         <v>0.0288917278871553</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -1834,12 +1896,12 @@
       <c r="E13" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="29" t="n">
         <v>0.02070141299528956</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1858,12 +1920,12 @@
       <c r="E14" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="27" t="n">
         <v>0.02022352920790581</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1882,12 +1944,12 @@
       <c r="E15" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="29" t="n">
         <v>0.01995543018813897</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1906,12 +1968,12 @@
       <c r="E16" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="27" t="n">
         <v>0.01936893477716919</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1930,12 +1992,12 @@
       <c r="E17" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="29" t="n">
         <v>0.01870151954139276</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1954,12 +2016,12 @@
       <c r="E18" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="27" t="n">
         <v>0.01831934915929091</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1978,12 +2040,12 @@
       <c r="E19" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="29" t="n">
         <v>0.01755093724054078</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2002,12 +2064,12 @@
       <c r="E20" s="6" t="n">
         <v>144</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="27" t="n">
         <v>0.01648100176461963</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -2026,12 +2088,12 @@
       <c r="E21" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="29" t="n">
         <v>0.01636529099829094</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2050,12 +2112,12 @@
       <c r="E22" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="27" t="n">
         <v>0.01570421577337497</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -2074,12 +2136,12 @@
       <c r="E23" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="29" t="n">
         <v>0.01458688903464856</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2098,12 +2160,12 @@
       <c r="E24" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="27" t="n">
         <v>0.01446202260660736</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -2122,12 +2184,12 @@
       <c r="E25" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="29" t="n">
         <v>0.01387085828780854</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2146,12 +2208,12 @@
       <c r="E26" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="27" t="n">
         <v>0.01353449247918622</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -2170,12 +2232,12 @@
       <c r="E27" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="29" t="n">
         <v>0.01322478678118691</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2194,12 +2256,12 @@
       <c r="E28" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="27" t="n">
         <v>0.01221804303197454</v>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -2218,12 +2280,12 @@
       <c r="E29" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F29" s="29" t="n">
         <v>0.01203418255067078</v>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2242,12 +2304,12 @@
       <c r="E30" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="27" t="n">
         <v>0.01088603297999195</v>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -2266,12 +2328,12 @@
       <c r="E31" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="29" t="n">
         <v>0.009524772867379495</v>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2290,12 +2352,12 @@
       <c r="E32" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="27" t="n">
         <v>0.008284223318821672</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -2314,12 +2376,12 @@
       <c r="E33" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="29" t="n">
         <v>0.008106041475219461</v>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2338,12 +2400,12 @@
       <c r="E34" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="27" t="n">
         <v>0.007713081461532159</v>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -2362,12 +2424,12 @@
       <c r="E35" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="F35" s="29" t="n">
         <v>0.007668937067392318</v>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2386,12 +2448,12 @@
       <c r="E36" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="27" t="n">
         <v>0.007574853639568111</v>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -2410,12 +2472,12 @@
       <c r="E37" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F37" s="13" t="n">
+      <c r="F37" s="29" t="n">
         <v>0.006960408678751375</v>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2434,12 +2496,12 @@
       <c r="E38" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="27" t="n">
         <v>0.006367612645054894</v>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="8" t="n">
+      <c r="A39" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -2458,12 +2520,12 @@
       <c r="E39" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="F39" s="29" t="n">
         <v>0.006318488119530872</v>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2482,12 +2544,12 @@
       <c r="E40" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="27" t="n">
         <v>0.005969634867773041</v>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -2506,12 +2568,12 @@
       <c r="E41" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="F41" s="29" t="n">
         <v>0.00505212841967909</v>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2530,12 +2592,12 @@
       <c r="E42" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F42" s="7" t="n">
+      <c r="F42" s="27" t="n">
         <v>0.005035481933411539</v>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="8" t="n">
+      <c r="A43" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -2554,12 +2616,12 @@
       <c r="E43" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="F43" s="29" t="n">
         <v>0.004822336827512594</v>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2578,12 +2640,12 @@
       <c r="E44" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="27" t="n">
         <v>0.004464324346745293</v>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="8" t="n">
+      <c r="A45" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -2602,12 +2664,12 @@
       <c r="E45" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F45" s="13" t="n">
+      <c r="F45" s="29" t="n">
         <v>0.004033871672385639</v>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2626,12 +2688,12 @@
       <c r="E46" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="27" t="n">
         <v>0.003976931143781494</v>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="8" t="n">
+      <c r="A47" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -2650,12 +2712,12 @@
       <c r="E47" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F47" s="13" t="n">
+      <c r="F47" s="29" t="n">
         <v>0.003587786548264043</v>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2674,12 +2736,12 @@
       <c r="E48" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="F48" s="27" t="n">
         <v>0.003583452707581172</v>
       </c>
     </row>
     <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="8" t="n">
+      <c r="A49" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -2698,12 +2760,12 @@
       <c r="E49" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F49" s="13" t="n">
+      <c r="F49" s="29" t="n">
         <v>0.003313689017007483</v>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2722,12 +2784,12 @@
       <c r="E50" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F50" s="27" t="n">
         <v>0.003007298650201687</v>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="8" t="n">
+      <c r="A51" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -2746,12 +2808,12 @@
       <c r="E51" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F51" s="13" t="n">
+      <c r="F51" s="29" t="n">
         <v>0.002930701150917258</v>
       </c>
     </row>
     <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2770,12 +2832,12 @@
       <c r="E52" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="F52" s="7" t="n">
+      <c r="F52" s="27" t="n">
         <v>0.002847437445660076</v>
       </c>
     </row>
     <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="8" t="n">
+      <c r="A53" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -2794,12 +2856,12 @@
       <c r="E53" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F53" s="13" t="n">
+      <c r="F53" s="29" t="n">
         <v>0.002823813123229756</v>
       </c>
     </row>
     <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2818,12 +2880,12 @@
       <c r="E54" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="F54" s="7" t="n">
+      <c r="F54" s="27" t="n">
         <v>0.002774171154813121</v>
       </c>
     </row>
     <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="8" t="n">
+      <c r="A55" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -2842,12 +2904,12 @@
       <c r="E55" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F55" s="13" t="n">
+      <c r="F55" s="29" t="n">
         <v>0.002539388655437964</v>
       </c>
     </row>
     <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2866,12 +2928,12 @@
       <c r="E56" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F56" s="7" t="n">
+      <c r="F56" s="27" t="n">
         <v>0.002239652535842587</v>
       </c>
     </row>
     <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="8" t="n">
+      <c r="A57" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -2890,12 +2952,12 @@
       <c r="E57" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F57" s="13" t="n">
+      <c r="F57" s="29" t="n">
         <v>0.002188033933727827</v>
       </c>
     </row>
     <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2914,12 +2976,12 @@
       <c r="E58" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F58" s="7" t="n">
+      <c r="F58" s="27" t="n">
         <v>0.002064816650434175</v>
       </c>
     </row>
     <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="8" t="n">
+      <c r="A59" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -2938,12 +3000,12 @@
       <c r="E59" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F59" s="13" t="n">
+      <c r="F59" s="29" t="n">
         <v>0.001981553980247612</v>
       </c>
     </row>
     <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2962,12 +3024,12 @@
       <c r="E60" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="F60" s="7" t="n">
+      <c r="F60" s="27" t="n">
         <v>0.001864990241795031</v>
       </c>
     </row>
     <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="8" t="n">
+      <c r="A61" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -2986,12 +3048,12 @@
       <c r="E61" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F61" s="13" t="n">
+      <c r="F61" s="29" t="n">
         <v>0.001858335809750572</v>
       </c>
     </row>
     <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3010,12 +3072,12 @@
       <c r="E62" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="F62" s="7" t="n">
+      <c r="F62" s="27" t="n">
         <v>0.001838347006519792</v>
       </c>
     </row>
     <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="8" t="n">
+      <c r="A63" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -3034,12 +3096,12 @@
       <c r="E63" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F63" s="13" t="n">
+      <c r="F63" s="29" t="n">
         <v>0.001823360071156196</v>
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3058,12 +3120,12 @@
       <c r="E64" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F64" s="27" t="n">
         <v>0.0017983852957856</v>
       </c>
     </row>
     <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="8" t="n">
+      <c r="A65" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -3082,12 +3144,12 @@
       <c r="E65" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F65" s="13" t="n">
+      <c r="F65" s="29" t="n">
         <v>0.00161521062270072</v>
       </c>
     </row>
     <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3106,12 +3168,12 @@
       <c r="E66" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F66" s="7" t="n">
+      <c r="F66" s="27" t="n">
         <v>0.001531962924071328</v>
       </c>
     </row>
     <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="8" t="n">
+      <c r="A67" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -3130,12 +3192,12 @@
       <c r="E67" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F67" s="13" t="n">
+      <c r="F67" s="29" t="n">
         <v>0.001453693841186994</v>
       </c>
     </row>
     <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3154,12 +3216,12 @@
       <c r="E68" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="27" t="n">
         <v>0.001343791521505552</v>
       </c>
     </row>
     <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="8" t="n">
+      <c r="A69" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -3178,12 +3240,12 @@
       <c r="E69" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F69" s="13" t="n">
+      <c r="F69" s="29" t="n">
         <v>0.001288840361664831</v>
       </c>
     </row>
     <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3202,12 +3264,12 @@
       <c r="E70" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F70" s="7" t="n">
+      <c r="F70" s="27" t="n">
         <v>0.0009091837779456971</v>
       </c>
     </row>
     <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="8" t="n">
+      <c r="A71" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -3226,12 +3288,12 @@
       <c r="E71" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F71" s="13" t="n">
+      <c r="F71" s="29" t="n">
         <v>0.0009058439007917856</v>
       </c>
     </row>
     <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3250,12 +3312,12 @@
       <c r="E72" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F72" s="7" t="n">
+      <c r="F72" s="27" t="n">
         <v>0.0008525654890054154</v>
       </c>
     </row>
     <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="8" t="n">
+      <c r="A73" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -3274,12 +3336,12 @@
       <c r="E73" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F73" s="13" t="n">
+      <c r="F73" s="29" t="n">
         <v>0.0006835516909963403</v>
       </c>
     </row>
     <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3298,12 +3360,12 @@
       <c r="E74" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="F74" s="7" t="n">
+      <c r="F74" s="27" t="n">
         <v>0.0005808047405722744</v>
       </c>
     </row>
     <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="8" t="n">
+      <c r="A75" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -3322,12 +3384,12 @@
       <c r="E75" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="13" t="n">
+      <c r="F75" s="29" t="n">
         <v>0.0005794805895157694</v>
       </c>
     </row>
     <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3346,12 +3408,12 @@
       <c r="E76" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F76" s="7" t="n">
+      <c r="F76" s="27" t="n">
         <v>0.0005594969801214898</v>
       </c>
     </row>
     <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="8" t="n">
+      <c r="A77" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -3370,12 +3432,12 @@
       <c r="E77" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F77" s="13" t="n">
+      <c r="F77" s="29" t="n">
         <v>0.0005295217970726194</v>
       </c>
     </row>
     <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3394,12 +3456,12 @@
       <c r="E78" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F78" s="7" t="n">
+      <c r="F78" s="27" t="n">
         <v>0.0004662475604487578</v>
       </c>
     </row>
     <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="8" t="n">
+      <c r="A79" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -3418,12 +3480,12 @@
       <c r="E79" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="13" t="n">
+      <c r="F79" s="29" t="n">
         <v>0.0004645822057559731</v>
       </c>
     </row>
     <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3442,12 +3504,12 @@
       <c r="E80" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F80" s="7" t="n">
+      <c r="F80" s="27" t="n">
         <v>0.0004262845928430992</v>
       </c>
     </row>
     <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="8" t="n">
+      <c r="A81" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -3466,12 +3528,12 @@
       <c r="E81" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F81" s="13" t="n">
+      <c r="F81" s="29" t="n">
         <v>0.0004262827445027077</v>
       </c>
     </row>
     <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3490,12 +3552,12 @@
       <c r="E82" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F82" s="7" t="n">
+      <c r="F82" s="27" t="n">
         <v>0.000415627635130955</v>
       </c>
     </row>
     <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="8" t="n">
+      <c r="A83" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -3514,12 +3576,12 @@
       <c r="E83" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F83" s="13" t="n">
+      <c r="F83" s="29" t="n">
         <v>0.0003396951872028085</v>
       </c>
     </row>
     <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3538,12 +3600,12 @@
       <c r="E84" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F84" s="7" t="n">
+      <c r="F84" s="27" t="n">
         <v>0.0003213783372400112</v>
       </c>
     </row>
     <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="8" t="n">
+      <c r="A85" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -3562,12 +3624,12 @@
       <c r="E85" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F85" s="13" t="n">
+      <c r="F85" s="29" t="n">
         <v>0.0003213783372400112</v>
       </c>
     </row>
     <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3586,12 +3648,12 @@
       <c r="E86" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F86" s="7" t="n">
+      <c r="F86" s="27" t="n">
         <v>0.0003213783372400112</v>
       </c>
     </row>
     <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="8" t="n">
+      <c r="A87" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -3610,12 +3672,12 @@
       <c r="E87" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F87" s="13" t="n">
+      <c r="F87" s="29" t="n">
         <v>0.0003030612839597709</v>
       </c>
     </row>
     <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3634,12 +3696,12 @@
       <c r="E88" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F88" s="7" t="n">
+      <c r="F88" s="27" t="n">
         <v>0.0003030612100261552</v>
       </c>
     </row>
     <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="8" t="n">
+      <c r="A89" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -3658,12 +3720,12 @@
       <c r="E89" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F89" s="13" t="n">
+      <c r="F89" s="29" t="n">
         <v>0.0002947353422490235</v>
       </c>
     </row>
     <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3682,12 +3744,12 @@
       <c r="E90" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F90" s="7" t="n">
+      <c r="F90" s="27" t="n">
         <v>0.0002664249963576282</v>
       </c>
     </row>
     <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="8" t="n">
+      <c r="A91" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -3706,12 +3768,12 @@
       <c r="E91" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F91" s="13" t="n">
+      <c r="F91" s="29" t="n">
         <v>0.0002531051900935926</v>
       </c>
     </row>
     <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3730,12 +3792,12 @@
       <c r="E92" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F92" s="7" t="n">
+      <c r="F92" s="27" t="n">
         <v>0.0002314584255315942</v>
       </c>
     </row>
     <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="8" t="n">
+      <c r="A93" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -3754,12 +3816,12 @@
       <c r="E93" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F93" s="13" t="n">
+      <c r="F93" s="29" t="n">
         <v>0.0002131413722513538</v>
       </c>
     </row>
     <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3778,12 +3840,12 @@
       <c r="E94" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F94" s="7" t="n">
+      <c r="F94" s="27" t="n">
         <v>0.0002024856898940798</v>
       </c>
     </row>
     <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="8" t="n">
+      <c r="A95" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -3802,12 +3864,12 @@
       <c r="E95" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="13" t="n">
+      <c r="F95" s="29" t="n">
         <v>0.0001981550283566829</v>
       </c>
     </row>
     <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3826,12 +3888,12 @@
       <c r="E96" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F96" s="7" t="n">
+      <c r="F96" s="27" t="n">
         <v>0.000183168684462012</v>
       </c>
     </row>
     <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="8" t="n">
+      <c r="A97" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -3850,12 +3912,12 @@
       <c r="E97" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F97" s="13" t="n">
+      <c r="F97" s="29" t="n">
         <v>0.00017484375933848</v>
       </c>
     </row>
     <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3874,12 +3936,12 @@
       <c r="E98" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F98" s="7" t="n">
+      <c r="F98" s="27" t="n">
         <v>0.0001648516311817717</v>
       </c>
     </row>
     <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="8" t="n">
+      <c r="A99" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -3898,12 +3960,12 @@
       <c r="E99" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="13" t="n">
+      <c r="F99" s="29" t="n">
         <v>0.0001265521699285062</v>
       </c>
     </row>
     <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3922,12 +3984,12 @@
       <c r="E100" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F100" s="7" t="n">
+      <c r="F100" s="27" t="n">
         <v>0.0001065679136150896</v>
       </c>
     </row>
     <row r="101" ht="17" customHeight="1">
-      <c r="A101" s="8" t="n">
+      <c r="A101" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -3946,12 +4008,12 @@
       <c r="E101" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F101" s="13" t="n">
+      <c r="F101" s="29" t="n">
         <v>9.324960450677114e-05</v>
       </c>
     </row>
     <row r="102" ht="17" customHeight="1">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3970,12 +4032,12 @@
       <c r="E102" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F102" s="7" t="n">
+      <c r="F102" s="27" t="n">
         <v>7.992593521131721e-05</v>
       </c>
     </row>
     <row r="103" ht="17" customHeight="1">
-      <c r="A103" s="8" t="n">
+      <c r="A103" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -3994,12 +4056,12 @@
       <c r="E103" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F103" s="13" t="n">
+      <c r="F103" s="29" t="n">
         <v>5.328395680754479e-05</v>
       </c>
     </row>
     <row r="104" ht="17" customHeight="1">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4018,12 +4080,12 @@
       <c r="E104" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F104" s="7" t="n">
+      <c r="F104" s="27" t="n">
         <v>2.664273622333294e-05</v>
       </c>
     </row>
     <row r="105" ht="17" customHeight="1">
-      <c r="A105" s="8" t="n">
+      <c r="A105" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -4042,7 +4104,7 @@
       <c r="E105" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F105" s="13" t="n">
+      <c r="F105" s="29" t="n">
         <v>2.66419784037724e-05</v>
       </c>
     </row>
@@ -4118,7 +4180,7 @@
       <c r="D3" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="E3" s="13" t="n">
+      <c r="E3" s="29" t="n">
         <v>0.08415142396242661</v>
       </c>
     </row>
@@ -4139,7 +4201,7 @@
       <c r="D4" s="24" t="n">
         <v>152</v>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="31" t="n">
         <v>0.0736295277357719</v>
       </c>
     </row>
@@ -4160,7 +4222,7 @@
       <c r="D5" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="29" t="n">
         <v>0.0559507071505526</v>
       </c>
     </row>
@@ -4181,7 +4243,7 @@
       <c r="D6" s="24" t="n">
         <v>143</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="31" t="n">
         <v>0.0504813420414981</v>
       </c>
     </row>
@@ -4202,7 +4264,7 @@
       <c r="D7" s="12" t="n">
         <v>129</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="29" t="n">
         <v>0.04680974475315458</v>
       </c>
     </row>
@@ -4223,7 +4285,7 @@
       <c r="D8" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="31" t="n">
         <v>0.04622520202139146</v>
       </c>
     </row>
@@ -4244,7 +4306,7 @@
       <c r="D9" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="29" t="n">
         <v>0.04549643569171836</v>
       </c>
     </row>
@@ -4265,7 +4327,7 @@
       <c r="D10" s="24" t="n">
         <v>119</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="31" t="n">
         <v>0.04316152083806643</v>
       </c>
     </row>
@@ -4286,7 +4348,7 @@
       <c r="D11" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="29" t="n">
         <v>0.03774595311781344</v>
       </c>
     </row>
@@ -4307,7 +4369,7 @@
       <c r="D12" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="31" t="n">
         <v>0.03269098285629893</v>
       </c>
     </row>
@@ -4328,7 +4390,7 @@
       <c r="D13" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="29" t="n">
         <v>0.02889172788715532</v>
       </c>
     </row>
@@ -4349,7 +4411,7 @@
       <c r="D14" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="31" t="n">
         <v>0.02070141299528958</v>
       </c>
     </row>
@@ -4370,7 +4432,7 @@
       <c r="D15" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="29" t="n">
         <v>0.02022352920790583</v>
       </c>
     </row>
@@ -4391,7 +4453,7 @@
       <c r="D16" s="24" t="n">
         <v>56</v>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="31" t="n">
         <v>0.01995543018813898</v>
       </c>
     </row>
@@ -4412,7 +4474,7 @@
       <c r="D17" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="29" t="n">
         <v>0.01936893477716921</v>
       </c>
     </row>
@@ -4433,7 +4495,7 @@
       <c r="D18" s="24" t="n">
         <v>81</v>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="31" t="n">
         <v>0.01870151954139278</v>
       </c>
     </row>
@@ -4454,7 +4516,7 @@
       <c r="D19" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="29" t="n">
         <v>0.01831934915929092</v>
       </c>
     </row>
@@ -4475,7 +4537,7 @@
       <c r="D20" s="24" t="n">
         <v>85</v>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="31" t="n">
         <v>0.0175509372405408</v>
       </c>
     </row>
@@ -4496,7 +4558,7 @@
       <c r="D21" s="12" t="n">
         <v>144</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="29" t="n">
         <v>0.01648100176461965</v>
       </c>
     </row>
@@ -4517,7 +4579,7 @@
       <c r="D22" s="24" t="n">
         <v>52</v>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="31" t="n">
         <v>0.01636529099829096</v>
       </c>
     </row>
@@ -4538,7 +4600,7 @@
       <c r="D23" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="29" t="n">
         <v>0.01570421577337498</v>
       </c>
     </row>
@@ -4559,7 +4621,7 @@
       <c r="D24" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="E24" s="25" t="n">
+      <c r="E24" s="31" t="n">
         <v>0.01458688903464858</v>
       </c>
     </row>
@@ -4580,7 +4642,7 @@
       <c r="D25" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="29" t="n">
         <v>0.01446202260660737</v>
       </c>
     </row>
@@ -4601,7 +4663,7 @@
       <c r="D26" s="24" t="n">
         <v>35</v>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="31" t="n">
         <v>0.01387085828780855</v>
       </c>
     </row>
@@ -4622,7 +4684,7 @@
       <c r="D27" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="29" t="n">
         <v>0.01353449247918623</v>
       </c>
     </row>
@@ -4643,7 +4705,7 @@
       <c r="D28" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="E28" s="25" t="n">
+      <c r="E28" s="31" t="n">
         <v>0.01322478678118692</v>
       </c>
     </row>
@@ -4664,7 +4726,7 @@
       <c r="D29" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="29" t="n">
         <v>0.01221804303197455</v>
       </c>
     </row>
@@ -4685,7 +4747,7 @@
       <c r="D30" s="24" t="n">
         <v>33</v>
       </c>
-      <c r="E30" s="25" t="n">
+      <c r="E30" s="31" t="n">
         <v>0.01203418255067079</v>
       </c>
     </row>
@@ -4706,7 +4768,7 @@
       <c r="D31" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="29" t="n">
         <v>0.01088603297999196</v>
       </c>
     </row>
@@ -4727,7 +4789,7 @@
       <c r="D32" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="E32" s="25" t="n">
+      <c r="E32" s="31" t="n">
         <v>0.009524772867379502</v>
       </c>
     </row>
@@ -4748,7 +4810,7 @@
       <c r="D33" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="29" t="n">
         <v>0.008284223318821679</v>
       </c>
     </row>
@@ -4769,7 +4831,7 @@
       <c r="D34" s="24" t="n">
         <v>61</v>
       </c>
-      <c r="E34" s="25" t="n">
+      <c r="E34" s="31" t="n">
         <v>0.008106041475219468</v>
       </c>
     </row>
@@ -4790,7 +4852,7 @@
       <c r="D35" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="29" t="n">
         <v>0.007713081461532166</v>
       </c>
     </row>
@@ -4811,7 +4873,7 @@
       <c r="D36" s="24" t="n">
         <v>67</v>
       </c>
-      <c r="E36" s="25" t="n">
+      <c r="E36" s="31" t="n">
         <v>0.007668937067392325</v>
       </c>
     </row>
@@ -4832,7 +4894,7 @@
       <c r="D37" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="29" t="n">
         <v>0.007574853639568118</v>
       </c>
     </row>
@@ -4853,7 +4915,7 @@
       <c r="D38" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E38" s="25" t="n">
+      <c r="E38" s="31" t="n">
         <v>0.006960408678751381</v>
       </c>
     </row>
@@ -4874,7 +4936,7 @@
       <c r="D39" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="29" t="n">
         <v>0.006367612645054899</v>
       </c>
     </row>
@@ -4895,7 +4957,7 @@
       <c r="D40" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="E40" s="25" t="n">
+      <c r="E40" s="31" t="n">
         <v>0.006318488119530878</v>
       </c>
     </row>
@@ -4916,7 +4978,7 @@
       <c r="D41" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="29" t="n">
         <v>0.005969634867773047</v>
       </c>
     </row>
@@ -4937,7 +4999,7 @@
       <c r="D42" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="E42" s="25" t="n">
+      <c r="E42" s="31" t="n">
         <v>0.005052128419679094</v>
       </c>
     </row>
@@ -4958,7 +5020,7 @@
       <c r="D43" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="E43" s="13" t="n">
+      <c r="E43" s="29" t="n">
         <v>0.005035481933411543</v>
       </c>
     </row>
@@ -4979,7 +5041,7 @@
       <c r="D44" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="E44" s="25" t="n">
+      <c r="E44" s="31" t="n">
         <v>0.004822336827512597</v>
       </c>
     </row>
@@ -5000,7 +5062,7 @@
       <c r="D45" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="E45" s="13" t="n">
+      <c r="E45" s="29" t="n">
         <v>0.004464324346745298</v>
       </c>
     </row>
@@ -5021,7 +5083,7 @@
       <c r="D46" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="E46" s="25" t="n">
+      <c r="E46" s="31" t="n">
         <v>0.004033871672385642</v>
       </c>
     </row>
@@ -5042,7 +5104,7 @@
       <c r="D47" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="E47" s="13" t="n">
+      <c r="E47" s="29" t="n">
         <v>0.003976931143781498</v>
       </c>
     </row>
@@ -5063,7 +5125,7 @@
       <c r="D48" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="E48" s="25" t="n">
+      <c r="E48" s="31" t="n">
         <v>0.003587786548264046</v>
       </c>
     </row>
@@ -5084,7 +5146,7 @@
       <c r="D49" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="E49" s="13" t="n">
+      <c r="E49" s="29" t="n">
         <v>0.003583452707581176</v>
       </c>
     </row>
@@ -5105,7 +5167,7 @@
       <c r="D50" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E50" s="25" t="n">
+      <c r="E50" s="31" t="n">
         <v>0.003313689017007486</v>
       </c>
     </row>
@@ -5126,7 +5188,7 @@
       <c r="D51" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="E51" s="13" t="n">
+      <c r="E51" s="29" t="n">
         <v>0.00300729865020169</v>
       </c>
     </row>
@@ -5147,7 +5209,7 @@
       <c r="D52" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E52" s="25" t="n">
+      <c r="E52" s="31" t="n">
         <v>0.00293070115091726</v>
       </c>
     </row>
@@ -5168,7 +5230,7 @@
       <c r="D53" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="E53" s="13" t="n">
+      <c r="E53" s="29" t="n">
         <v>0.002847437445660078</v>
       </c>
     </row>
@@ -5189,7 +5251,7 @@
       <c r="D54" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E54" s="25" t="n">
+      <c r="E54" s="31" t="n">
         <v>0.002823813123229759</v>
       </c>
     </row>
@@ -5210,7 +5272,7 @@
       <c r="D55" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="E55" s="13" t="n">
+      <c r="E55" s="29" t="n">
         <v>0.002774171154813124</v>
       </c>
     </row>
@@ -5231,7 +5293,7 @@
       <c r="D56" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="E56" s="25" t="n">
+      <c r="E56" s="31" t="n">
         <v>0.002539388655437966</v>
       </c>
     </row>
@@ -5252,7 +5314,7 @@
       <c r="D57" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E57" s="13" t="n">
+      <c r="E57" s="29" t="n">
         <v>0.002239652535842589</v>
       </c>
     </row>
@@ -5273,7 +5335,7 @@
       <c r="D58" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="E58" s="25" t="n">
+      <c r="E58" s="31" t="n">
         <v>0.002188033933727829</v>
       </c>
     </row>
@@ -5294,7 +5356,7 @@
       <c r="D59" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="E59" s="13" t="n">
+      <c r="E59" s="29" t="n">
         <v>0.002064816650434177</v>
       </c>
     </row>
@@ -5315,7 +5377,7 @@
       <c r="D60" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="E60" s="25" t="n">
+      <c r="E60" s="31" t="n">
         <v>0.001981553980247614</v>
       </c>
     </row>
@@ -5336,7 +5398,7 @@
       <c r="D61" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="E61" s="13" t="n">
+      <c r="E61" s="29" t="n">
         <v>0.001864990241795033</v>
       </c>
     </row>
@@ -5357,7 +5419,7 @@
       <c r="D62" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="E62" s="25" t="n">
+      <c r="E62" s="31" t="n">
         <v>0.001858335809750574</v>
       </c>
     </row>
@@ -5378,7 +5440,7 @@
       <c r="D63" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="E63" s="13" t="n">
+      <c r="E63" s="29" t="n">
         <v>0.001838347006519794</v>
       </c>
     </row>
@@ -5399,7 +5461,7 @@
       <c r="D64" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="E64" s="25" t="n">
+      <c r="E64" s="31" t="n">
         <v>0.001823360071156198</v>
       </c>
     </row>
@@ -5420,7 +5482,7 @@
       <c r="D65" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E65" s="13" t="n">
+      <c r="E65" s="29" t="n">
         <v>0.001798385295785602</v>
       </c>
     </row>
@@ -5441,7 +5503,7 @@
       <c r="D66" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E66" s="25" t="n">
+      <c r="E66" s="31" t="n">
         <v>0.001615210622700721</v>
       </c>
     </row>
@@ -5462,7 +5524,7 @@
       <c r="D67" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="E67" s="13" t="n">
+      <c r="E67" s="29" t="n">
         <v>0.00153196292407133</v>
       </c>
     </row>
@@ -5483,7 +5545,7 @@
       <c r="D68" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="E68" s="25" t="n">
+      <c r="E68" s="31" t="n">
         <v>0.001453693841186996</v>
       </c>
     </row>
@@ -5504,7 +5566,7 @@
       <c r="D69" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="E69" s="13" t="n">
+      <c r="E69" s="29" t="n">
         <v>0.001343791521505554</v>
       </c>
     </row>
@@ -5525,7 +5587,7 @@
       <c r="D70" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="E70" s="25" t="n">
+      <c r="E70" s="31" t="n">
         <v>0.001288840361664832</v>
       </c>
     </row>
@@ -5546,7 +5608,7 @@
       <c r="D71" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="E71" s="13" t="n">
+      <c r="E71" s="29" t="n">
         <v>0.0009091837779456978</v>
       </c>
     </row>
@@ -5567,7 +5629,7 @@
       <c r="D72" s="24" t="n">
         <v>34</v>
       </c>
-      <c r="E72" s="25" t="n">
+      <c r="E72" s="31" t="n">
         <v>0.0009058439007917864</v>
       </c>
     </row>
@@ -5588,7 +5650,7 @@
       <c r="D73" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="E73" s="13" t="n">
+      <c r="E73" s="29" t="n">
         <v>0.0008525654890054161</v>
       </c>
     </row>
@@ -5609,7 +5671,7 @@
       <c r="D74" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="E74" s="25" t="n">
+      <c r="E74" s="31" t="n">
         <v>0.0006835516909963409</v>
       </c>
     </row>
@@ -5630,7 +5692,7 @@
       <c r="D75" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="E75" s="13" t="n">
+      <c r="E75" s="29" t="n">
         <v>0.0005808047405722748</v>
       </c>
     </row>
@@ -5651,7 +5713,7 @@
       <c r="D76" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E76" s="25" t="n">
+      <c r="E76" s="31" t="n">
         <v>0.0005794805895157699</v>
       </c>
     </row>
@@ -5672,7 +5734,7 @@
       <c r="D77" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="E77" s="13" t="n">
+      <c r="E77" s="29" t="n">
         <v>0.0005594969801214903</v>
       </c>
     </row>
@@ -5693,7 +5755,7 @@
       <c r="D78" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="E78" s="25" t="n">
+      <c r="E78" s="31" t="n">
         <v>0.0005295217970726198</v>
       </c>
     </row>
@@ -5714,7 +5776,7 @@
       <c r="D79" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="13" t="n">
+      <c r="E79" s="29" t="n">
         <v>0.0004662475604487582</v>
       </c>
     </row>
@@ -5735,7 +5797,7 @@
       <c r="D80" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E80" s="25" t="n">
+      <c r="E80" s="31" t="n">
         <v>0.0004645822057559735</v>
       </c>
     </row>
@@ -5756,7 +5818,7 @@
       <c r="D81" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E81" s="13" t="n">
+      <c r="E81" s="29" t="n">
         <v>0.0004262845928430996</v>
       </c>
     </row>
@@ -5777,7 +5839,7 @@
       <c r="D82" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="E82" s="25" t="n">
+      <c r="E82" s="31" t="n">
         <v>0.0004262827445027081</v>
       </c>
     </row>
@@ -5798,7 +5860,7 @@
       <c r="D83" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E83" s="13" t="n">
+      <c r="E83" s="29" t="n">
         <v>0.0004156276351309554</v>
       </c>
     </row>
@@ -5819,7 +5881,7 @@
       <c r="D84" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="E84" s="25" t="n">
+      <c r="E84" s="31" t="n">
         <v>0.0003396951872028088</v>
       </c>
     </row>
@@ -5840,7 +5902,7 @@
       <c r="D85" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E85" s="13" t="n">
+      <c r="E85" s="29" t="n">
         <v>0.0003213783372400115</v>
       </c>
     </row>
@@ -5861,7 +5923,7 @@
       <c r="D86" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E86" s="25" t="n">
+      <c r="E86" s="31" t="n">
         <v>0.0003213783372400115</v>
       </c>
     </row>
@@ -5882,7 +5944,7 @@
       <c r="D87" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E87" s="13" t="n">
+      <c r="E87" s="29" t="n">
         <v>0.0003213783372400115</v>
       </c>
     </row>
@@ -5903,7 +5965,7 @@
       <c r="D88" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E88" s="25" t="n">
+      <c r="E88" s="31" t="n">
         <v>0.0003030612839597711</v>
       </c>
     </row>
@@ -5924,7 +5986,7 @@
       <c r="D89" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E89" s="13" t="n">
+      <c r="E89" s="29" t="n">
         <v>0.0003030612100261555</v>
       </c>
     </row>
@@ -5945,7 +6007,7 @@
       <c r="D90" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="E90" s="25" t="n">
+      <c r="E90" s="31" t="n">
         <v>0.0002947353422490237</v>
       </c>
     </row>
@@ -5966,7 +6028,7 @@
       <c r="D91" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E91" s="13" t="n">
+      <c r="E91" s="29" t="n">
         <v>0.0002664249963576284</v>
       </c>
     </row>
@@ -5987,7 +6049,7 @@
       <c r="D92" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="E92" s="25" t="n">
+      <c r="E92" s="31" t="n">
         <v>0.0002531051900935928</v>
       </c>
     </row>
@@ -6008,7 +6070,7 @@
       <c r="D93" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E93" s="13" t="n">
+      <c r="E93" s="29" t="n">
         <v>0.0002314584255315944</v>
       </c>
     </row>
@@ -6029,7 +6091,7 @@
       <c r="D94" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E94" s="25" t="n">
+      <c r="E94" s="31" t="n">
         <v>0.000213141372251354</v>
       </c>
     </row>
@@ -6050,7 +6112,7 @@
       <c r="D95" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E95" s="13" t="n">
+      <c r="E95" s="29" t="n">
         <v>0.00020248568989408</v>
       </c>
     </row>
@@ -6071,7 +6133,7 @@
       <c r="D96" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E96" s="25" t="n">
+      <c r="E96" s="31" t="n">
         <v>0.0001981550283566831</v>
       </c>
     </row>
@@ -6092,7 +6154,7 @@
       <c r="D97" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E97" s="13" t="n">
+      <c r="E97" s="29" t="n">
         <v>0.0001831686844620122</v>
       </c>
     </row>
@@ -6113,7 +6175,7 @@
       <c r="D98" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E98" s="25" t="n">
+      <c r="E98" s="31" t="n">
         <v>0.0001748437593384801</v>
       </c>
     </row>
@@ -6134,7 +6196,7 @@
       <c r="D99" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E99" s="13" t="n">
+      <c r="E99" s="29" t="n">
         <v>0.0001648516311817718</v>
       </c>
     </row>
@@ -6155,7 +6217,7 @@
       <c r="D100" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E100" s="25" t="n">
+      <c r="E100" s="31" t="n">
         <v>0.0001265521699285063</v>
       </c>
     </row>
@@ -6176,7 +6238,7 @@
       <c r="D101" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="E101" s="13" t="n">
+      <c r="E101" s="29" t="n">
         <v>0.0001065679136150897</v>
       </c>
     </row>
@@ -6197,7 +6259,7 @@
       <c r="D102" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E102" s="25" t="n">
+      <c r="E102" s="31" t="n">
         <v>9.324960450677122e-05</v>
       </c>
     </row>
@@ -6218,7 +6280,7 @@
       <c r="D103" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="E103" s="13" t="n">
+      <c r="E103" s="29" t="n">
         <v>7.992593521131727e-05</v>
       </c>
     </row>
@@ -6239,7 +6301,7 @@
       <c r="D104" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="E104" s="25" t="n">
+      <c r="E104" s="31" t="n">
         <v>5.328395680754484e-05</v>
       </c>
     </row>
@@ -6260,7 +6322,7 @@
       <c r="D105" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E105" s="13" t="n">
+      <c r="E105" s="29" t="n">
         <v>2.664273622333296e-05</v>
       </c>
     </row>
@@ -6281,7 +6343,7 @@
       <c r="D106" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E106" s="25" t="n">
+      <c r="E106" s="31" t="n">
         <v>2.664197840377242e-05</v>
       </c>
     </row>
@@ -6302,7 +6364,7 @@
       <c r="D107" s="19" t="n">
         <v>3017</v>
       </c>
-      <c r="E107" s="20" t="inlineStr">
+      <c r="E107" s="30" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -6366,7 +6428,7 @@
       </c>
     </row>
     <row r="2" ht="17" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -6397,7 +6459,7 @@
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -6428,7 +6490,7 @@
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -6459,7 +6521,7 @@
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -6490,7 +6552,7 @@
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -6521,7 +6583,7 @@
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -6552,7 +6614,7 @@
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -6583,7 +6645,7 @@
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -6614,7 +6676,7 @@
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -6645,7 +6707,7 @@
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -6676,7 +6738,7 @@
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -6707,7 +6769,7 @@
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -6738,7 +6800,7 @@
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -6769,7 +6831,7 @@
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -6800,7 +6862,7 @@
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -6831,7 +6893,7 @@
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -6862,7 +6924,7 @@
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -6893,7 +6955,7 @@
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -6924,7 +6986,7 @@
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -6955,7 +7017,7 @@
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -6986,7 +7048,7 @@
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -7017,7 +7079,7 @@
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -7048,7 +7110,7 @@
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -7079,7 +7141,7 @@
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -7110,7 +7172,7 @@
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -7141,7 +7203,7 @@
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -7172,7 +7234,7 @@
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -7203,7 +7265,7 @@
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -7234,7 +7296,7 @@
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -7265,7 +7327,7 @@
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -7296,7 +7358,7 @@
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7327,7 +7389,7 @@
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -7358,7 +7420,7 @@
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7389,7 +7451,7 @@
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -7420,7 +7482,7 @@
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -7451,7 +7513,7 @@
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -7482,7 +7544,7 @@
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -7513,7 +7575,7 @@
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="8" t="n">
+      <c r="A39" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -7544,7 +7606,7 @@
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -7575,7 +7637,7 @@
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -7606,7 +7668,7 @@
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -7637,7 +7699,7 @@
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="8" t="n">
+      <c r="A43" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -7668,7 +7730,7 @@
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -7699,7 +7761,7 @@
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="8" t="n">
+      <c r="A45" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -7730,7 +7792,7 @@
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -7761,7 +7823,7 @@
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="8" t="n">
+      <c r="A47" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -7792,7 +7854,7 @@
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -7823,7 +7885,7 @@
       </c>
     </row>
     <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="8" t="n">
+      <c r="A49" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -7854,7 +7916,7 @@
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -7885,7 +7947,7 @@
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="8" t="n">
+      <c r="A51" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -7916,7 +7978,7 @@
       </c>
     </row>
     <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -7947,7 +8009,7 @@
       </c>
     </row>
     <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="8" t="n">
+      <c r="A53" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -7978,7 +8040,7 @@
       </c>
     </row>
     <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -8009,7 +8071,7 @@
       </c>
     </row>
     <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="8" t="n">
+      <c r="A55" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -8040,7 +8102,7 @@
       </c>
     </row>
     <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -8071,7 +8133,7 @@
       </c>
     </row>
     <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="8" t="n">
+      <c r="A57" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -8102,7 +8164,7 @@
       </c>
     </row>
     <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -8133,7 +8195,7 @@
       </c>
     </row>
     <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="8" t="n">
+      <c r="A59" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -8164,7 +8226,7 @@
       </c>
     </row>
     <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -8195,7 +8257,7 @@
       </c>
     </row>
     <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="8" t="n">
+      <c r="A61" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -8226,7 +8288,7 @@
       </c>
     </row>
     <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -8257,7 +8319,7 @@
       </c>
     </row>
     <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="8" t="n">
+      <c r="A63" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -8288,7 +8350,7 @@
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -8319,7 +8381,7 @@
       </c>
     </row>
     <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="8" t="n">
+      <c r="A65" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -8350,7 +8412,7 @@
       </c>
     </row>
     <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -8381,7 +8443,7 @@
       </c>
     </row>
     <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="8" t="n">
+      <c r="A67" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -8412,7 +8474,7 @@
       </c>
     </row>
     <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -8443,7 +8505,7 @@
       </c>
     </row>
     <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="8" t="n">
+      <c r="A69" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -8474,7 +8536,7 @@
       </c>
     </row>
     <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -8505,7 +8567,7 @@
       </c>
     </row>
     <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="8" t="n">
+      <c r="A71" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -8536,7 +8598,7 @@
       </c>
     </row>
     <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -8567,7 +8629,7 @@
       </c>
     </row>
     <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="8" t="n">
+      <c r="A73" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -8598,7 +8660,7 @@
       </c>
     </row>
     <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -8629,7 +8691,7 @@
       </c>
     </row>
     <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="8" t="n">
+      <c r="A75" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -8660,7 +8722,7 @@
       </c>
     </row>
     <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -8691,7 +8753,7 @@
       </c>
     </row>
     <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="8" t="n">
+      <c r="A77" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -8722,7 +8784,7 @@
       </c>
     </row>
     <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -8753,7 +8815,7 @@
       </c>
     </row>
     <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="8" t="n">
+      <c r="A79" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -8784,7 +8846,7 @@
       </c>
     </row>
     <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -8815,7 +8877,7 @@
       </c>
     </row>
     <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="8" t="n">
+      <c r="A81" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -8846,7 +8908,7 @@
       </c>
     </row>
     <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -8877,7 +8939,7 @@
       </c>
     </row>
     <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="8" t="n">
+      <c r="A83" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -8908,7 +8970,7 @@
       </c>
     </row>
     <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -8939,7 +9001,7 @@
       </c>
     </row>
     <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="8" t="n">
+      <c r="A85" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -8970,7 +9032,7 @@
       </c>
     </row>
     <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -9001,7 +9063,7 @@
       </c>
     </row>
     <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="8" t="n">
+      <c r="A87" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -9032,7 +9094,7 @@
       </c>
     </row>
     <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -9063,7 +9125,7 @@
       </c>
     </row>
     <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="8" t="n">
+      <c r="A89" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -9094,7 +9156,7 @@
       </c>
     </row>
     <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -9125,7 +9187,7 @@
       </c>
     </row>
     <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="8" t="n">
+      <c r="A91" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -9156,7 +9218,7 @@
       </c>
     </row>
     <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -9187,7 +9249,7 @@
       </c>
     </row>
     <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="8" t="n">
+      <c r="A93" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -9218,7 +9280,7 @@
       </c>
     </row>
     <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -9249,7 +9311,7 @@
       </c>
     </row>
     <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="8" t="n">
+      <c r="A95" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -9280,7 +9342,7 @@
       </c>
     </row>
     <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9311,7 +9373,7 @@
       </c>
     </row>
     <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="8" t="n">
+      <c r="A97" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -9342,7 +9404,7 @@
       </c>
     </row>
     <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9373,7 +9435,7 @@
       </c>
     </row>
     <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="8" t="n">
+      <c r="A99" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -9404,7 +9466,7 @@
       </c>
     </row>
     <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9435,7 +9497,7 @@
       </c>
     </row>
     <row r="101" ht="17" customHeight="1">
-      <c r="A101" s="8" t="n">
+      <c r="A101" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -9466,7 +9528,7 @@
       </c>
     </row>
     <row r="102" ht="17" customHeight="1">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -9497,7 +9559,7 @@
       </c>
     </row>
     <row r="103" ht="17" customHeight="1">
-      <c r="A103" s="8" t="n">
+      <c r="A103" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -9528,7 +9590,7 @@
       </c>
     </row>
     <row r="104" ht="17" customHeight="1">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -9559,7 +9621,7 @@
       </c>
     </row>
     <row r="105" ht="17" customHeight="1">
-      <c r="A105" s="8" t="n">
+      <c r="A105" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -9590,7 +9652,7 @@
       </c>
     </row>
     <row r="106" ht="17" customHeight="1">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -9621,7 +9683,7 @@
       </c>
     </row>
     <row r="107" ht="17" customHeight="1">
-      <c r="A107" s="8" t="n">
+      <c r="A107" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -9652,7 +9714,7 @@
       </c>
     </row>
     <row r="108" ht="17" customHeight="1">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -9683,7 +9745,7 @@
       </c>
     </row>
     <row r="109" ht="17" customHeight="1">
-      <c r="A109" s="8" t="n">
+      <c r="A109" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -9714,7 +9776,7 @@
       </c>
     </row>
     <row r="110" ht="17" customHeight="1">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -9745,7 +9807,7 @@
       </c>
     </row>
     <row r="111" ht="17" customHeight="1">
-      <c r="A111" s="8" t="n">
+      <c r="A111" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -9776,7 +9838,7 @@
       </c>
     </row>
     <row r="112" ht="17" customHeight="1">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -9807,7 +9869,7 @@
       </c>
     </row>
     <row r="113" ht="17" customHeight="1">
-      <c r="A113" s="8" t="n">
+      <c r="A113" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -9838,7 +9900,7 @@
       </c>
     </row>
     <row r="114" ht="17" customHeight="1">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -9869,7 +9931,7 @@
       </c>
     </row>
     <row r="115" ht="17" customHeight="1">
-      <c r="A115" s="8" t="n">
+      <c r="A115" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -9900,7 +9962,7 @@
       </c>
     </row>
     <row r="116" ht="17" customHeight="1">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -9931,7 +9993,7 @@
       </c>
     </row>
     <row r="117" ht="17" customHeight="1">
-      <c r="A117" s="8" t="n">
+      <c r="A117" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -9962,7 +10024,7 @@
       </c>
     </row>
     <row r="118" ht="17" customHeight="1">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -9993,7 +10055,7 @@
       </c>
     </row>
     <row r="119" ht="17" customHeight="1">
-      <c r="A119" s="8" t="n">
+      <c r="A119" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -10024,7 +10086,7 @@
       </c>
     </row>
     <row r="120" ht="17" customHeight="1">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -10055,7 +10117,7 @@
       </c>
     </row>
     <row r="121" ht="17" customHeight="1">
-      <c r="A121" s="8" t="n">
+      <c r="A121" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -10086,7 +10148,7 @@
       </c>
     </row>
     <row r="122" ht="17" customHeight="1">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -10117,7 +10179,7 @@
       </c>
     </row>
     <row r="123" ht="17" customHeight="1">
-      <c r="A123" s="8" t="n">
+      <c r="A123" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -10148,7 +10210,7 @@
       </c>
     </row>
     <row r="124" ht="17" customHeight="1">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -10179,7 +10241,7 @@
       </c>
     </row>
     <row r="125" ht="17" customHeight="1">
-      <c r="A125" s="8" t="n">
+      <c r="A125" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -10210,7 +10272,7 @@
       </c>
     </row>
     <row r="126" ht="17" customHeight="1">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -10241,7 +10303,7 @@
       </c>
     </row>
     <row r="127" ht="17" customHeight="1">
-      <c r="A127" s="8" t="n">
+      <c r="A127" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -10272,7 +10334,7 @@
       </c>
     </row>
     <row r="128" ht="17" customHeight="1">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -10303,7 +10365,7 @@
       </c>
     </row>
     <row r="129" ht="17" customHeight="1">
-      <c r="A129" s="8" t="n">
+      <c r="A129" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -10334,7 +10396,7 @@
       </c>
     </row>
     <row r="130" ht="17" customHeight="1">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -10365,7 +10427,7 @@
       </c>
     </row>
     <row r="131" ht="17" customHeight="1">
-      <c r="A131" s="8" t="n">
+      <c r="A131" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -10396,7 +10458,7 @@
       </c>
     </row>
     <row r="132" ht="17" customHeight="1">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -10427,7 +10489,7 @@
       </c>
     </row>
     <row r="133" ht="17" customHeight="1">
-      <c r="A133" s="8" t="n">
+      <c r="A133" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -10458,7 +10520,7 @@
       </c>
     </row>
     <row r="134" ht="17" customHeight="1">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -10489,7 +10551,7 @@
       </c>
     </row>
     <row r="135" ht="17" customHeight="1">
-      <c r="A135" s="8" t="n">
+      <c r="A135" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -10520,7 +10582,7 @@
       </c>
     </row>
     <row r="136" ht="17" customHeight="1">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -10551,7 +10613,7 @@
       </c>
     </row>
     <row r="137" ht="17" customHeight="1">
-      <c r="A137" s="8" t="n">
+      <c r="A137" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -10582,7 +10644,7 @@
       </c>
     </row>
     <row r="138" ht="17" customHeight="1">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -10613,7 +10675,7 @@
       </c>
     </row>
     <row r="139" ht="17" customHeight="1">
-      <c r="A139" s="8" t="n">
+      <c r="A139" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -10644,7 +10706,7 @@
       </c>
     </row>
     <row r="140" ht="17" customHeight="1">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -10675,7 +10737,7 @@
       </c>
     </row>
     <row r="141" ht="17" customHeight="1">
-      <c r="A141" s="8" t="n">
+      <c r="A141" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -10706,7 +10768,7 @@
       </c>
     </row>
     <row r="142" ht="17" customHeight="1">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -10737,7 +10799,7 @@
       </c>
     </row>
     <row r="143" ht="17" customHeight="1">
-      <c r="A143" s="8" t="n">
+      <c r="A143" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -10768,7 +10830,7 @@
       </c>
     </row>
     <row r="144" ht="17" customHeight="1">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -10799,7 +10861,7 @@
       </c>
     </row>
     <row r="145" ht="17" customHeight="1">
-      <c r="A145" s="8" t="n">
+      <c r="A145" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -10830,7 +10892,7 @@
       </c>
     </row>
     <row r="146" ht="17" customHeight="1">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -10861,7 +10923,7 @@
       </c>
     </row>
     <row r="147" ht="17" customHeight="1">
-      <c r="A147" s="8" t="n">
+      <c r="A147" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -10892,7 +10954,7 @@
       </c>
     </row>
     <row r="148" ht="17" customHeight="1">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -10923,7 +10985,7 @@
       </c>
     </row>
     <row r="149" ht="17" customHeight="1">
-      <c r="A149" s="8" t="n">
+      <c r="A149" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -10954,7 +11016,7 @@
       </c>
     </row>
     <row r="150" ht="17" customHeight="1">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -10985,7 +11047,7 @@
       </c>
     </row>
     <row r="151" ht="17" customHeight="1">
-      <c r="A151" s="8" t="n">
+      <c r="A151" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -11016,7 +11078,7 @@
       </c>
     </row>
     <row r="152" ht="17" customHeight="1">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -11047,7 +11109,7 @@
       </c>
     </row>
     <row r="153" ht="17" customHeight="1">
-      <c r="A153" s="8" t="n">
+      <c r="A153" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -11078,7 +11140,7 @@
       </c>
     </row>
     <row r="154" ht="17" customHeight="1">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -11109,7 +11171,7 @@
       </c>
     </row>
     <row r="155" ht="17" customHeight="1">
-      <c r="A155" s="8" t="n">
+      <c r="A155" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -11140,7 +11202,7 @@
       </c>
     </row>
     <row r="156" ht="17" customHeight="1">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -11171,7 +11233,7 @@
       </c>
     </row>
     <row r="157" ht="17" customHeight="1">
-      <c r="A157" s="8" t="n">
+      <c r="A157" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -11202,7 +11264,7 @@
       </c>
     </row>
     <row r="158" ht="17" customHeight="1">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -11233,7 +11295,7 @@
       </c>
     </row>
     <row r="159" ht="17" customHeight="1">
-      <c r="A159" s="8" t="n">
+      <c r="A159" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -11264,7 +11326,7 @@
       </c>
     </row>
     <row r="160" ht="17" customHeight="1">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -11295,7 +11357,7 @@
       </c>
     </row>
     <row r="161" ht="17" customHeight="1">
-      <c r="A161" s="8" t="n">
+      <c r="A161" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -11326,7 +11388,7 @@
       </c>
     </row>
     <row r="162" ht="17" customHeight="1">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -11357,7 +11419,7 @@
       </c>
     </row>
     <row r="163" ht="17" customHeight="1">
-      <c r="A163" s="8" t="n">
+      <c r="A163" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -11388,7 +11450,7 @@
       </c>
     </row>
     <row r="164" ht="17" customHeight="1">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -11419,7 +11481,7 @@
       </c>
     </row>
     <row r="165" ht="17" customHeight="1">
-      <c r="A165" s="8" t="n">
+      <c r="A165" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -11450,7 +11512,7 @@
       </c>
     </row>
     <row r="166" ht="17" customHeight="1">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -11481,7 +11543,7 @@
       </c>
     </row>
     <row r="167" ht="17" customHeight="1">
-      <c r="A167" s="8" t="n">
+      <c r="A167" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -11512,7 +11574,7 @@
       </c>
     </row>
     <row r="168" ht="17" customHeight="1">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -11543,7 +11605,7 @@
       </c>
     </row>
     <row r="169" ht="17" customHeight="1">
-      <c r="A169" s="8" t="n">
+      <c r="A169" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -11574,7 +11636,7 @@
       </c>
     </row>
     <row r="170" ht="17" customHeight="1">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -11605,7 +11667,7 @@
       </c>
     </row>
     <row r="171" ht="17" customHeight="1">
-      <c r="A171" s="8" t="n">
+      <c r="A171" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -11636,7 +11698,7 @@
       </c>
     </row>
     <row r="172" ht="17" customHeight="1">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -11667,7 +11729,7 @@
       </c>
     </row>
     <row r="173" ht="17" customHeight="1">
-      <c r="A173" s="8" t="n">
+      <c r="A173" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -11698,7 +11760,7 @@
       </c>
     </row>
     <row r="174" ht="17" customHeight="1">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -11729,7 +11791,7 @@
       </c>
     </row>
     <row r="175" ht="17" customHeight="1">
-      <c r="A175" s="8" t="n">
+      <c r="A175" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -11760,7 +11822,7 @@
       </c>
     </row>
     <row r="176" ht="17" customHeight="1">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -11791,7 +11853,7 @@
       </c>
     </row>
     <row r="177" ht="17" customHeight="1">
-      <c r="A177" s="8" t="n">
+      <c r="A177" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -11822,7 +11884,7 @@
       </c>
     </row>
     <row r="178" ht="17" customHeight="1">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -11853,7 +11915,7 @@
       </c>
     </row>
     <row r="179" ht="17" customHeight="1">
-      <c r="A179" s="8" t="n">
+      <c r="A179" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -11884,7 +11946,7 @@
       </c>
     </row>
     <row r="180" ht="17" customHeight="1">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -11915,7 +11977,7 @@
       </c>
     </row>
     <row r="181" ht="17" customHeight="1">
-      <c r="A181" s="8" t="n">
+      <c r="A181" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -11946,7 +12008,7 @@
       </c>
     </row>
     <row r="182" ht="17" customHeight="1">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -11977,7 +12039,7 @@
       </c>
     </row>
     <row r="183" ht="17" customHeight="1">
-      <c r="A183" s="8" t="n">
+      <c r="A183" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -12008,7 +12070,7 @@
       </c>
     </row>
     <row r="184" ht="17" customHeight="1">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -12039,7 +12101,7 @@
       </c>
     </row>
     <row r="185" ht="17" customHeight="1">
-      <c r="A185" s="8" t="n">
+      <c r="A185" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -12070,7 +12132,7 @@
       </c>
     </row>
     <row r="186" ht="17" customHeight="1">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -12101,7 +12163,7 @@
       </c>
     </row>
     <row r="187" ht="17" customHeight="1">
-      <c r="A187" s="8" t="n">
+      <c r="A187" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -12132,7 +12194,7 @@
       </c>
     </row>
     <row r="188" ht="17" customHeight="1">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -12163,7 +12225,7 @@
       </c>
     </row>
     <row r="189" ht="17" customHeight="1">
-      <c r="A189" s="8" t="n">
+      <c r="A189" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -12194,7 +12256,7 @@
       </c>
     </row>
     <row r="190" ht="17" customHeight="1">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -12225,7 +12287,7 @@
       </c>
     </row>
     <row r="191" ht="17" customHeight="1">
-      <c r="A191" s="8" t="n">
+      <c r="A191" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -12256,7 +12318,7 @@
       </c>
     </row>
     <row r="192" ht="17" customHeight="1">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -12287,7 +12349,7 @@
       </c>
     </row>
     <row r="193" ht="17" customHeight="1">
-      <c r="A193" s="8" t="n">
+      <c r="A193" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -12318,7 +12380,7 @@
       </c>
     </row>
     <row r="194" ht="17" customHeight="1">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -12349,7 +12411,7 @@
       </c>
     </row>
     <row r="195" ht="17" customHeight="1">
-      <c r="A195" s="8" t="n">
+      <c r="A195" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -12380,7 +12442,7 @@
       </c>
     </row>
     <row r="196" ht="17" customHeight="1">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -12411,7 +12473,7 @@
       </c>
     </row>
     <row r="197" ht="17" customHeight="1">
-      <c r="A197" s="8" t="n">
+      <c r="A197" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -12442,7 +12504,7 @@
       </c>
     </row>
     <row r="198" ht="17" customHeight="1">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -12473,7 +12535,7 @@
       </c>
     </row>
     <row r="199" ht="17" customHeight="1">
-      <c r="A199" s="8" t="n">
+      <c r="A199" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -12504,7 +12566,7 @@
       </c>
     </row>
     <row r="200" ht="17" customHeight="1">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -12535,7 +12597,7 @@
       </c>
     </row>
     <row r="201" ht="17" customHeight="1">
-      <c r="A201" s="8" t="n">
+      <c r="A201" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -12566,7 +12628,7 @@
       </c>
     </row>
     <row r="202" ht="17" customHeight="1">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -12597,7 +12659,7 @@
       </c>
     </row>
     <row r="203" ht="17" customHeight="1">
-      <c r="A203" s="8" t="n">
+      <c r="A203" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -12628,7 +12690,7 @@
       </c>
     </row>
     <row r="204" ht="17" customHeight="1">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -12659,7 +12721,7 @@
       </c>
     </row>
     <row r="205" ht="17" customHeight="1">
-      <c r="A205" s="8" t="n">
+      <c r="A205" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -12690,7 +12752,7 @@
       </c>
     </row>
     <row r="206" ht="17" customHeight="1">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -12721,7 +12783,7 @@
       </c>
     </row>
     <row r="207" ht="17" customHeight="1">
-      <c r="A207" s="8" t="n">
+      <c r="A207" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -12752,7 +12814,7 @@
       </c>
     </row>
     <row r="208" ht="17" customHeight="1">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -12783,7 +12845,7 @@
       </c>
     </row>
     <row r="209" ht="17" customHeight="1">
-      <c r="A209" s="8" t="n">
+      <c r="A209" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -12814,7 +12876,7 @@
       </c>
     </row>
     <row r="210" ht="17" customHeight="1">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -12845,7 +12907,7 @@
       </c>
     </row>
     <row r="211" ht="17" customHeight="1">
-      <c r="A211" s="8" t="n">
+      <c r="A211" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -12876,7 +12938,7 @@
       </c>
     </row>
     <row r="212" ht="17" customHeight="1">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -12907,7 +12969,7 @@
       </c>
     </row>
     <row r="213" ht="17" customHeight="1">
-      <c r="A213" s="8" t="n">
+      <c r="A213" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -12938,7 +13000,7 @@
       </c>
     </row>
     <row r="214" ht="17" customHeight="1">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -12969,7 +13031,7 @@
       </c>
     </row>
     <row r="215" ht="17" customHeight="1">
-      <c r="A215" s="8" t="n">
+      <c r="A215" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -13000,7 +13062,7 @@
       </c>
     </row>
     <row r="216" ht="17" customHeight="1">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -13031,7 +13093,7 @@
       </c>
     </row>
     <row r="217" ht="17" customHeight="1">
-      <c r="A217" s="8" t="n">
+      <c r="A217" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -13062,7 +13124,7 @@
       </c>
     </row>
     <row r="218" ht="17" customHeight="1">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -13093,7 +13155,7 @@
       </c>
     </row>
     <row r="219" ht="17" customHeight="1">
-      <c r="A219" s="8" t="n">
+      <c r="A219" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -13124,7 +13186,7 @@
       </c>
     </row>
     <row r="220" ht="17" customHeight="1">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -13155,7 +13217,7 @@
       </c>
     </row>
     <row r="221" ht="17" customHeight="1">
-      <c r="A221" s="8" t="n">
+      <c r="A221" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -13186,7 +13248,7 @@
       </c>
     </row>
     <row r="222" ht="17" customHeight="1">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -13217,7 +13279,7 @@
       </c>
     </row>
     <row r="223" ht="17" customHeight="1">
-      <c r="A223" s="8" t="n">
+      <c r="A223" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -13248,7 +13310,7 @@
       </c>
     </row>
     <row r="224" ht="17" customHeight="1">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -13279,7 +13341,7 @@
       </c>
     </row>
     <row r="225" ht="17" customHeight="1">
-      <c r="A225" s="8" t="n">
+      <c r="A225" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -13310,7 +13372,7 @@
       </c>
     </row>
     <row r="226" ht="17" customHeight="1">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -13341,7 +13403,7 @@
       </c>
     </row>
     <row r="227" ht="17" customHeight="1">
-      <c r="A227" s="8" t="n">
+      <c r="A227" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -13372,7 +13434,7 @@
       </c>
     </row>
     <row r="228" ht="17" customHeight="1">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -13403,7 +13465,7 @@
       </c>
     </row>
     <row r="229" ht="17" customHeight="1">
-      <c r="A229" s="8" t="n">
+      <c r="A229" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B229" s="9" t="inlineStr">
@@ -13434,7 +13496,7 @@
       </c>
     </row>
     <row r="230" ht="17" customHeight="1">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -13465,7 +13527,7 @@
       </c>
     </row>
     <row r="231" ht="17" customHeight="1">
-      <c r="A231" s="8" t="n">
+      <c r="A231" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B231" s="9" t="inlineStr">
@@ -13496,7 +13558,7 @@
       </c>
     </row>
     <row r="232" ht="17" customHeight="1">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -13527,7 +13589,7 @@
       </c>
     </row>
     <row r="233" ht="17" customHeight="1">
-      <c r="A233" s="8" t="n">
+      <c r="A233" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B233" s="9" t="inlineStr">
@@ -13558,7 +13620,7 @@
       </c>
     </row>
     <row r="234" ht="17" customHeight="1">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -13589,7 +13651,7 @@
       </c>
     </row>
     <row r="235" ht="17" customHeight="1">
-      <c r="A235" s="8" t="n">
+      <c r="A235" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B235" s="9" t="inlineStr">
@@ -13620,7 +13682,7 @@
       </c>
     </row>
     <row r="236" ht="17" customHeight="1">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -13651,7 +13713,7 @@
       </c>
     </row>
     <row r="237" ht="17" customHeight="1">
-      <c r="A237" s="8" t="n">
+      <c r="A237" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B237" s="9" t="inlineStr">
@@ -13682,7 +13744,7 @@
       </c>
     </row>
     <row r="238" ht="17" customHeight="1">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -13713,7 +13775,7 @@
       </c>
     </row>
     <row r="239" ht="17" customHeight="1">
-      <c r="A239" s="8" t="n">
+      <c r="A239" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B239" s="9" t="inlineStr">
@@ -13744,7 +13806,7 @@
       </c>
     </row>
     <row r="240" ht="17" customHeight="1">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -13775,7 +13837,7 @@
       </c>
     </row>
     <row r="241" ht="17" customHeight="1">
-      <c r="A241" s="8" t="n">
+      <c r="A241" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B241" s="9" t="inlineStr">
@@ -13806,7 +13868,7 @@
       </c>
     </row>
     <row r="242" ht="17" customHeight="1">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -13837,7 +13899,7 @@
       </c>
     </row>
     <row r="243" ht="17" customHeight="1">
-      <c r="A243" s="8" t="n">
+      <c r="A243" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B243" s="9" t="inlineStr">
@@ -13868,7 +13930,7 @@
       </c>
     </row>
     <row r="244" ht="17" customHeight="1">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -13899,7 +13961,7 @@
       </c>
     </row>
     <row r="245" ht="17" customHeight="1">
-      <c r="A245" s="8" t="n">
+      <c r="A245" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B245" s="9" t="inlineStr">
@@ -13930,7 +13992,7 @@
       </c>
     </row>
     <row r="246" ht="17" customHeight="1">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -13961,7 +14023,7 @@
       </c>
     </row>
     <row r="247" ht="17" customHeight="1">
-      <c r="A247" s="8" t="n">
+      <c r="A247" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B247" s="9" t="inlineStr">
@@ -13992,7 +14054,7 @@
       </c>
     </row>
     <row r="248" ht="17" customHeight="1">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -14023,7 +14085,7 @@
       </c>
     </row>
     <row r="249" ht="17" customHeight="1">
-      <c r="A249" s="8" t="n">
+      <c r="A249" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B249" s="9" t="inlineStr">
@@ -14054,7 +14116,7 @@
       </c>
     </row>
     <row r="250" ht="17" customHeight="1">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -14085,7 +14147,7 @@
       </c>
     </row>
     <row r="251" ht="17" customHeight="1">
-      <c r="A251" s="8" t="n">
+      <c r="A251" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B251" s="9" t="inlineStr">
@@ -14116,7 +14178,7 @@
       </c>
     </row>
     <row r="252" ht="17" customHeight="1">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -14147,7 +14209,7 @@
       </c>
     </row>
     <row r="253" ht="17" customHeight="1">
-      <c r="A253" s="8" t="n">
+      <c r="A253" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B253" s="9" t="inlineStr">
@@ -14178,7 +14240,7 @@
       </c>
     </row>
     <row r="254" ht="17" customHeight="1">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -14209,7 +14271,7 @@
       </c>
     </row>
     <row r="255" ht="17" customHeight="1">
-      <c r="A255" s="8" t="n">
+      <c r="A255" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B255" s="9" t="inlineStr">
@@ -14240,7 +14302,7 @@
       </c>
     </row>
     <row r="256" ht="17" customHeight="1">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -14271,7 +14333,7 @@
       </c>
     </row>
     <row r="257" ht="17" customHeight="1">
-      <c r="A257" s="8" t="n">
+      <c r="A257" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B257" s="9" t="inlineStr">
@@ -14302,7 +14364,7 @@
       </c>
     </row>
     <row r="258" ht="17" customHeight="1">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -14333,7 +14395,7 @@
       </c>
     </row>
     <row r="259" ht="17" customHeight="1">
-      <c r="A259" s="8" t="n">
+      <c r="A259" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B259" s="9" t="inlineStr">
@@ -14364,7 +14426,7 @@
       </c>
     </row>
     <row r="260" ht="17" customHeight="1">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -14395,7 +14457,7 @@
       </c>
     </row>
     <row r="261" ht="17" customHeight="1">
-      <c r="A261" s="8" t="n">
+      <c r="A261" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B261" s="9" t="inlineStr">
@@ -14426,7 +14488,7 @@
       </c>
     </row>
     <row r="262" ht="17" customHeight="1">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -14457,7 +14519,7 @@
       </c>
     </row>
     <row r="263" ht="17" customHeight="1">
-      <c r="A263" s="8" t="n">
+      <c r="A263" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B263" s="9" t="inlineStr">
@@ -14488,7 +14550,7 @@
       </c>
     </row>
     <row r="264" ht="17" customHeight="1">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -14519,7 +14581,7 @@
       </c>
     </row>
     <row r="265" ht="17" customHeight="1">
-      <c r="A265" s="8" t="n">
+      <c r="A265" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B265" s="9" t="inlineStr">
@@ -14550,7 +14612,7 @@
       </c>
     </row>
     <row r="266" ht="17" customHeight="1">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -14581,7 +14643,7 @@
       </c>
     </row>
     <row r="267" ht="17" customHeight="1">
-      <c r="A267" s="8" t="n">
+      <c r="A267" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B267" s="9" t="inlineStr">
@@ -14612,7 +14674,7 @@
       </c>
     </row>
     <row r="268" ht="17" customHeight="1">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -14643,7 +14705,7 @@
       </c>
     </row>
     <row r="269" ht="17" customHeight="1">
-      <c r="A269" s="8" t="n">
+      <c r="A269" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B269" s="9" t="inlineStr">
@@ -14674,7 +14736,7 @@
       </c>
     </row>
     <row r="270" ht="17" customHeight="1">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -14705,7 +14767,7 @@
       </c>
     </row>
     <row r="271" ht="17" customHeight="1">
-      <c r="A271" s="8" t="n">
+      <c r="A271" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B271" s="9" t="inlineStr">
@@ -14736,7 +14798,7 @@
       </c>
     </row>
     <row r="272" ht="17" customHeight="1">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -14767,7 +14829,7 @@
       </c>
     </row>
     <row r="273" ht="17" customHeight="1">
-      <c r="A273" s="8" t="n">
+      <c r="A273" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B273" s="9" t="inlineStr">
@@ -14798,7 +14860,7 @@
       </c>
     </row>
     <row r="274" ht="17" customHeight="1">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -14829,7 +14891,7 @@
       </c>
     </row>
     <row r="275" ht="17" customHeight="1">
-      <c r="A275" s="8" t="n">
+      <c r="A275" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B275" s="9" t="inlineStr">
@@ -14860,7 +14922,7 @@
       </c>
     </row>
     <row r="276" ht="17" customHeight="1">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -14891,7 +14953,7 @@
       </c>
     </row>
     <row r="277" ht="17" customHeight="1">
-      <c r="A277" s="8" t="n">
+      <c r="A277" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B277" s="9" t="inlineStr">
@@ -14922,7 +14984,7 @@
       </c>
     </row>
     <row r="278" ht="17" customHeight="1">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -14953,7 +15015,7 @@
       </c>
     </row>
     <row r="279" ht="17" customHeight="1">
-      <c r="A279" s="8" t="n">
+      <c r="A279" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B279" s="9" t="inlineStr">
@@ -14984,7 +15046,7 @@
       </c>
     </row>
     <row r="280" ht="17" customHeight="1">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -15015,7 +15077,7 @@
       </c>
     </row>
     <row r="281" ht="17" customHeight="1">
-      <c r="A281" s="8" t="n">
+      <c r="A281" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B281" s="9" t="inlineStr">
@@ -15046,7 +15108,7 @@
       </c>
     </row>
     <row r="282" ht="17" customHeight="1">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -15077,7 +15139,7 @@
       </c>
     </row>
     <row r="283" ht="17" customHeight="1">
-      <c r="A283" s="8" t="n">
+      <c r="A283" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B283" s="9" t="inlineStr">
@@ -15108,7 +15170,7 @@
       </c>
     </row>
     <row r="284" ht="17" customHeight="1">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -15139,7 +15201,7 @@
       </c>
     </row>
     <row r="285" ht="17" customHeight="1">
-      <c r="A285" s="8" t="n">
+      <c r="A285" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B285" s="9" t="inlineStr">
@@ -15170,7 +15232,7 @@
       </c>
     </row>
     <row r="286" ht="17" customHeight="1">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -15201,7 +15263,7 @@
       </c>
     </row>
     <row r="287" ht="17" customHeight="1">
-      <c r="A287" s="8" t="n">
+      <c r="A287" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B287" s="9" t="inlineStr">
@@ -15232,7 +15294,7 @@
       </c>
     </row>
     <row r="288" ht="17" customHeight="1">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -15263,7 +15325,7 @@
       </c>
     </row>
     <row r="289" ht="17" customHeight="1">
-      <c r="A289" s="8" t="n">
+      <c r="A289" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B289" s="9" t="inlineStr">
@@ -15294,7 +15356,7 @@
       </c>
     </row>
     <row r="290" ht="17" customHeight="1">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -15325,7 +15387,7 @@
       </c>
     </row>
     <row r="291" ht="17" customHeight="1">
-      <c r="A291" s="8" t="n">
+      <c r="A291" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B291" s="9" t="inlineStr">
@@ -15356,7 +15418,7 @@
       </c>
     </row>
     <row r="292" ht="17" customHeight="1">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -15387,7 +15449,7 @@
       </c>
     </row>
     <row r="293" ht="17" customHeight="1">
-      <c r="A293" s="8" t="n">
+      <c r="A293" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B293" s="9" t="inlineStr">
@@ -15418,7 +15480,7 @@
       </c>
     </row>
     <row r="294" ht="17" customHeight="1">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -15449,7 +15511,7 @@
       </c>
     </row>
     <row r="295" ht="17" customHeight="1">
-      <c r="A295" s="8" t="n">
+      <c r="A295" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B295" s="9" t="inlineStr">
@@ -15480,7 +15542,7 @@
       </c>
     </row>
     <row r="296" ht="17" customHeight="1">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -15511,7 +15573,7 @@
       </c>
     </row>
     <row r="297" ht="17" customHeight="1">
-      <c r="A297" s="8" t="n">
+      <c r="A297" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B297" s="9" t="inlineStr">
@@ -15542,7 +15604,7 @@
       </c>
     </row>
     <row r="298" ht="17" customHeight="1">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -15573,7 +15635,7 @@
       </c>
     </row>
     <row r="299" ht="17" customHeight="1">
-      <c r="A299" s="8" t="n">
+      <c r="A299" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B299" s="9" t="inlineStr">
@@ -15604,7 +15666,7 @@
       </c>
     </row>
     <row r="300" ht="17" customHeight="1">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -15635,7 +15697,7 @@
       </c>
     </row>
     <row r="301" ht="17" customHeight="1">
-      <c r="A301" s="8" t="n">
+      <c r="A301" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B301" s="9" t="inlineStr">
@@ -15666,7 +15728,7 @@
       </c>
     </row>
     <row r="302" ht="17" customHeight="1">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B302" s="3" t="inlineStr">
@@ -15697,7 +15759,7 @@
       </c>
     </row>
     <row r="303" ht="17" customHeight="1">
-      <c r="A303" s="8" t="n">
+      <c r="A303" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B303" s="9" t="inlineStr">
@@ -15728,7 +15790,7 @@
       </c>
     </row>
     <row r="304" ht="17" customHeight="1">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -15759,7 +15821,7 @@
       </c>
     </row>
     <row r="305" ht="17" customHeight="1">
-      <c r="A305" s="8" t="n">
+      <c r="A305" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B305" s="9" t="inlineStr">
@@ -15790,7 +15852,7 @@
       </c>
     </row>
     <row r="306" ht="17" customHeight="1">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -15821,7 +15883,7 @@
       </c>
     </row>
     <row r="307" ht="17" customHeight="1">
-      <c r="A307" s="8" t="n">
+      <c r="A307" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B307" s="9" t="inlineStr">
@@ -15852,7 +15914,7 @@
       </c>
     </row>
     <row r="308" ht="17" customHeight="1">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B308" s="3" t="inlineStr">
@@ -15883,7 +15945,7 @@
       </c>
     </row>
     <row r="309" ht="17" customHeight="1">
-      <c r="A309" s="8" t="n">
+      <c r="A309" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B309" s="9" t="inlineStr">
@@ -15914,7 +15976,7 @@
       </c>
     </row>
     <row r="310" ht="17" customHeight="1">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B310" s="3" t="inlineStr">
@@ -15945,7 +16007,7 @@
       </c>
     </row>
     <row r="311" ht="17" customHeight="1">
-      <c r="A311" s="8" t="n">
+      <c r="A311" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B311" s="9" t="inlineStr">
@@ -15976,7 +16038,7 @@
       </c>
     </row>
     <row r="312" ht="17" customHeight="1">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -16007,7 +16069,7 @@
       </c>
     </row>
     <row r="313" ht="17" customHeight="1">
-      <c r="A313" s="8" t="n">
+      <c r="A313" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B313" s="9" t="inlineStr">
@@ -16038,7 +16100,7 @@
       </c>
     </row>
     <row r="314" ht="17" customHeight="1">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B314" s="3" t="inlineStr">
@@ -16069,7 +16131,7 @@
       </c>
     </row>
     <row r="315" ht="17" customHeight="1">
-      <c r="A315" s="8" t="n">
+      <c r="A315" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B315" s="9" t="inlineStr">
@@ -16100,7 +16162,7 @@
       </c>
     </row>
     <row r="316" ht="17" customHeight="1">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B316" s="3" t="inlineStr">
@@ -16131,7 +16193,7 @@
       </c>
     </row>
     <row r="317" ht="17" customHeight="1">
-      <c r="A317" s="8" t="n">
+      <c r="A317" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B317" s="9" t="inlineStr">
@@ -16162,7 +16224,7 @@
       </c>
     </row>
     <row r="318" ht="17" customHeight="1">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B318" s="3" t="inlineStr">
@@ -16193,7 +16255,7 @@
       </c>
     </row>
     <row r="319" ht="17" customHeight="1">
-      <c r="A319" s="8" t="n">
+      <c r="A319" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B319" s="9" t="inlineStr">
@@ -16224,7 +16286,7 @@
       </c>
     </row>
     <row r="320" ht="17" customHeight="1">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B320" s="3" t="inlineStr">
@@ -16255,7 +16317,7 @@
       </c>
     </row>
     <row r="321" ht="17" customHeight="1">
-      <c r="A321" s="8" t="n">
+      <c r="A321" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B321" s="9" t="inlineStr">
@@ -16286,7 +16348,7 @@
       </c>
     </row>
     <row r="322" ht="17" customHeight="1">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B322" s="3" t="inlineStr">
@@ -16317,7 +16379,7 @@
       </c>
     </row>
     <row r="323" ht="17" customHeight="1">
-      <c r="A323" s="8" t="n">
+      <c r="A323" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B323" s="9" t="inlineStr">
@@ -16348,7 +16410,7 @@
       </c>
     </row>
     <row r="324" ht="17" customHeight="1">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B324" s="3" t="inlineStr">
@@ -16379,7 +16441,7 @@
       </c>
     </row>
     <row r="325" ht="17" customHeight="1">
-      <c r="A325" s="8" t="n">
+      <c r="A325" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B325" s="9" t="inlineStr">
@@ -16410,7 +16472,7 @@
       </c>
     </row>
     <row r="326" ht="17" customHeight="1">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B326" s="3" t="inlineStr">
@@ -16441,7 +16503,7 @@
       </c>
     </row>
     <row r="327" ht="17" customHeight="1">
-      <c r="A327" s="8" t="n">
+      <c r="A327" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B327" s="9" t="inlineStr">
@@ -16472,7 +16534,7 @@
       </c>
     </row>
     <row r="328" ht="17" customHeight="1">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B328" s="3" t="inlineStr">
@@ -16503,7 +16565,7 @@
       </c>
     </row>
     <row r="329" ht="17" customHeight="1">
-      <c r="A329" s="8" t="n">
+      <c r="A329" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B329" s="9" t="inlineStr">
@@ -16534,7 +16596,7 @@
       </c>
     </row>
     <row r="330" ht="17" customHeight="1">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B330" s="3" t="inlineStr">
@@ -16565,7 +16627,7 @@
       </c>
     </row>
     <row r="331" ht="17" customHeight="1">
-      <c r="A331" s="8" t="n">
+      <c r="A331" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B331" s="9" t="inlineStr">
@@ -16596,7 +16658,7 @@
       </c>
     </row>
     <row r="332" ht="17" customHeight="1">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B332" s="3" t="inlineStr">
@@ -16627,7 +16689,7 @@
       </c>
     </row>
     <row r="333" ht="17" customHeight="1">
-      <c r="A333" s="8" t="n">
+      <c r="A333" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B333" s="9" t="inlineStr">
@@ -16658,7 +16720,7 @@
       </c>
     </row>
     <row r="334" ht="17" customHeight="1">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B334" s="3" t="inlineStr">
@@ -16689,7 +16751,7 @@
       </c>
     </row>
     <row r="335" ht="17" customHeight="1">
-      <c r="A335" s="8" t="n">
+      <c r="A335" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B335" s="9" t="inlineStr">
@@ -16720,7 +16782,7 @@
       </c>
     </row>
     <row r="336" ht="17" customHeight="1">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B336" s="3" t="inlineStr">
@@ -16751,7 +16813,7 @@
       </c>
     </row>
     <row r="337" ht="17" customHeight="1">
-      <c r="A337" s="8" t="n">
+      <c r="A337" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -16782,7 +16844,7 @@
       </c>
     </row>
     <row r="338" ht="17" customHeight="1">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B338" s="3" t="inlineStr">
@@ -16813,7 +16875,7 @@
       </c>
     </row>
     <row r="339" ht="17" customHeight="1">
-      <c r="A339" s="8" t="n">
+      <c r="A339" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -16844,7 +16906,7 @@
       </c>
     </row>
     <row r="340" ht="17" customHeight="1">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B340" s="3" t="inlineStr">
@@ -16875,7 +16937,7 @@
       </c>
     </row>
     <row r="341" ht="17" customHeight="1">
-      <c r="A341" s="8" t="n">
+      <c r="A341" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -16906,7 +16968,7 @@
       </c>
     </row>
     <row r="342" ht="17" customHeight="1">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B342" s="3" t="inlineStr">
@@ -16937,7 +16999,7 @@
       </c>
     </row>
     <row r="343" ht="17" customHeight="1">
-      <c r="A343" s="8" t="n">
+      <c r="A343" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -16968,7 +17030,7 @@
       </c>
     </row>
     <row r="344" ht="17" customHeight="1">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B344" s="3" t="inlineStr">
@@ -16999,7 +17061,7 @@
       </c>
     </row>
     <row r="345" ht="17" customHeight="1">
-      <c r="A345" s="8" t="n">
+      <c r="A345" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -17030,7 +17092,7 @@
       </c>
     </row>
     <row r="346" ht="17" customHeight="1">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B346" s="3" t="inlineStr">
@@ -17061,7 +17123,7 @@
       </c>
     </row>
     <row r="347" ht="17" customHeight="1">
-      <c r="A347" s="8" t="n">
+      <c r="A347" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -17092,7 +17154,7 @@
       </c>
     </row>
     <row r="348" ht="17" customHeight="1">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B348" s="3" t="inlineStr">
@@ -17123,7 +17185,7 @@
       </c>
     </row>
     <row r="349" ht="17" customHeight="1">
-      <c r="A349" s="8" t="n">
+      <c r="A349" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -17154,7 +17216,7 @@
       </c>
     </row>
     <row r="350" ht="17" customHeight="1">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B350" s="3" t="inlineStr">
@@ -17185,7 +17247,7 @@
       </c>
     </row>
     <row r="351" ht="17" customHeight="1">
-      <c r="A351" s="8" t="n">
+      <c r="A351" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -17216,7 +17278,7 @@
       </c>
     </row>
     <row r="352" ht="17" customHeight="1">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B352" s="3" t="inlineStr">
@@ -17247,7 +17309,7 @@
       </c>
     </row>
     <row r="353" ht="17" customHeight="1">
-      <c r="A353" s="8" t="n">
+      <c r="A353" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -17278,7 +17340,7 @@
       </c>
     </row>
     <row r="354" ht="17" customHeight="1">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B354" s="3" t="inlineStr">
@@ -17309,7 +17371,7 @@
       </c>
     </row>
     <row r="355" ht="17" customHeight="1">
-      <c r="A355" s="8" t="n">
+      <c r="A355" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -17340,7 +17402,7 @@
       </c>
     </row>
     <row r="356" ht="17" customHeight="1">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B356" s="3" t="inlineStr">
@@ -17371,7 +17433,7 @@
       </c>
     </row>
     <row r="357" ht="17" customHeight="1">
-      <c r="A357" s="8" t="n">
+      <c r="A357" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -17402,7 +17464,7 @@
       </c>
     </row>
     <row r="358" ht="17" customHeight="1">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B358" s="3" t="inlineStr">
@@ -17433,7 +17495,7 @@
       </c>
     </row>
     <row r="359" ht="17" customHeight="1">
-      <c r="A359" s="8" t="n">
+      <c r="A359" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -17464,7 +17526,7 @@
       </c>
     </row>
     <row r="360" ht="17" customHeight="1">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B360" s="3" t="inlineStr">
@@ -17495,7 +17557,7 @@
       </c>
     </row>
     <row r="361" ht="17" customHeight="1">
-      <c r="A361" s="8" t="n">
+      <c r="A361" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -17526,7 +17588,7 @@
       </c>
     </row>
     <row r="362" ht="17" customHeight="1">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B362" s="3" t="inlineStr">
@@ -17557,7 +17619,7 @@
       </c>
     </row>
     <row r="363" ht="17" customHeight="1">
-      <c r="A363" s="8" t="n">
+      <c r="A363" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -17588,7 +17650,7 @@
       </c>
     </row>
     <row r="364" ht="17" customHeight="1">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B364" s="3" t="inlineStr">
@@ -17619,7 +17681,7 @@
       </c>
     </row>
     <row r="365" ht="17" customHeight="1">
-      <c r="A365" s="8" t="n">
+      <c r="A365" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -17650,7 +17712,7 @@
       </c>
     </row>
     <row r="366" ht="17" customHeight="1">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B366" s="3" t="inlineStr">
@@ -17681,7 +17743,7 @@
       </c>
     </row>
     <row r="367" ht="17" customHeight="1">
-      <c r="A367" s="8" t="n">
+      <c r="A367" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -17712,7 +17774,7 @@
       </c>
     </row>
     <row r="368" ht="17" customHeight="1">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B368" s="3" t="inlineStr">
@@ -17743,7 +17805,7 @@
       </c>
     </row>
     <row r="369" ht="17" customHeight="1">
-      <c r="A369" s="8" t="n">
+      <c r="A369" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -17774,7 +17836,7 @@
       </c>
     </row>
     <row r="370" ht="17" customHeight="1">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B370" s="3" t="inlineStr">
@@ -17805,7 +17867,7 @@
       </c>
     </row>
     <row r="371" ht="17" customHeight="1">
-      <c r="A371" s="8" t="n">
+      <c r="A371" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -17836,7 +17898,7 @@
       </c>
     </row>
     <row r="372" ht="17" customHeight="1">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B372" s="3" t="inlineStr">
@@ -17867,7 +17929,7 @@
       </c>
     </row>
     <row r="373" ht="17" customHeight="1">
-      <c r="A373" s="8" t="n">
+      <c r="A373" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -17898,7 +17960,7 @@
       </c>
     </row>
     <row r="374" ht="17" customHeight="1">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B374" s="3" t="inlineStr">
@@ -17929,7 +17991,7 @@
       </c>
     </row>
     <row r="375" ht="17" customHeight="1">
-      <c r="A375" s="8" t="n">
+      <c r="A375" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -17960,7 +18022,7 @@
       </c>
     </row>
     <row r="376" ht="17" customHeight="1">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B376" s="3" t="inlineStr">
@@ -17991,7 +18053,7 @@
       </c>
     </row>
     <row r="377" ht="17" customHeight="1">
-      <c r="A377" s="8" t="n">
+      <c r="A377" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -18022,7 +18084,7 @@
       </c>
     </row>
     <row r="378" ht="17" customHeight="1">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B378" s="3" t="inlineStr">
@@ -18053,7 +18115,7 @@
       </c>
     </row>
     <row r="379" ht="17" customHeight="1">
-      <c r="A379" s="8" t="n">
+      <c r="A379" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -18084,7 +18146,7 @@
       </c>
     </row>
     <row r="380" ht="17" customHeight="1">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B380" s="3" t="inlineStr">
@@ -18115,7 +18177,7 @@
       </c>
     </row>
     <row r="381" ht="17" customHeight="1">
-      <c r="A381" s="8" t="n">
+      <c r="A381" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B381" s="9" t="inlineStr">
@@ -18146,7 +18208,7 @@
       </c>
     </row>
     <row r="382" ht="17" customHeight="1">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B382" s="3" t="inlineStr">
@@ -18177,7 +18239,7 @@
       </c>
     </row>
     <row r="383" ht="17" customHeight="1">
-      <c r="A383" s="8" t="n">
+      <c r="A383" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B383" s="9" t="inlineStr">
@@ -18208,7 +18270,7 @@
       </c>
     </row>
     <row r="384" ht="17" customHeight="1">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B384" s="3" t="inlineStr">
@@ -18239,7 +18301,7 @@
       </c>
     </row>
     <row r="385" ht="17" customHeight="1">
-      <c r="A385" s="8" t="n">
+      <c r="A385" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B385" s="9" t="inlineStr">
@@ -18270,7 +18332,7 @@
       </c>
     </row>
     <row r="386" ht="17" customHeight="1">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B386" s="3" t="inlineStr">
@@ -18301,7 +18363,7 @@
       </c>
     </row>
     <row r="387" ht="17" customHeight="1">
-      <c r="A387" s="8" t="n">
+      <c r="A387" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B387" s="9" t="inlineStr">
@@ -18332,7 +18394,7 @@
       </c>
     </row>
     <row r="388" ht="17" customHeight="1">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B388" s="3" t="inlineStr">
@@ -18363,7 +18425,7 @@
       </c>
     </row>
     <row r="389" ht="17" customHeight="1">
-      <c r="A389" s="8" t="n">
+      <c r="A389" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B389" s="9" t="inlineStr">
@@ -18394,7 +18456,7 @@
       </c>
     </row>
     <row r="390" ht="17" customHeight="1">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B390" s="3" t="inlineStr">
@@ -18425,7 +18487,7 @@
       </c>
     </row>
     <row r="391" ht="17" customHeight="1">
-      <c r="A391" s="8" t="n">
+      <c r="A391" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B391" s="9" t="inlineStr">
@@ -18456,7 +18518,7 @@
       </c>
     </row>
     <row r="392" ht="17" customHeight="1">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B392" s="3" t="inlineStr">
@@ -18487,7 +18549,7 @@
       </c>
     </row>
     <row r="393" ht="17" customHeight="1">
-      <c r="A393" s="8" t="n">
+      <c r="A393" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B393" s="9" t="inlineStr">
@@ -18518,7 +18580,7 @@
       </c>
     </row>
     <row r="394" ht="17" customHeight="1">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B394" s="3" t="inlineStr">
@@ -18549,7 +18611,7 @@
       </c>
     </row>
     <row r="395" ht="17" customHeight="1">
-      <c r="A395" s="8" t="n">
+      <c r="A395" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B395" s="9" t="inlineStr">
@@ -18580,7 +18642,7 @@
       </c>
     </row>
     <row r="396" ht="17" customHeight="1">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B396" s="3" t="inlineStr">
@@ -18611,7 +18673,7 @@
       </c>
     </row>
     <row r="397" ht="17" customHeight="1">
-      <c r="A397" s="8" t="n">
+      <c r="A397" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B397" s="9" t="inlineStr">
@@ -18642,7 +18704,7 @@
       </c>
     </row>
     <row r="398" ht="17" customHeight="1">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B398" s="3" t="inlineStr">
@@ -18673,7 +18735,7 @@
       </c>
     </row>
     <row r="399" ht="17" customHeight="1">
-      <c r="A399" s="8" t="n">
+      <c r="A399" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B399" s="9" t="inlineStr">
@@ -18704,7 +18766,7 @@
       </c>
     </row>
     <row r="400" ht="17" customHeight="1">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B400" s="3" t="inlineStr">
@@ -18735,7 +18797,7 @@
       </c>
     </row>
     <row r="401" ht="17" customHeight="1">
-      <c r="A401" s="8" t="n">
+      <c r="A401" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B401" s="9" t="inlineStr">
@@ -18766,7 +18828,7 @@
       </c>
     </row>
     <row r="402" ht="17" customHeight="1">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B402" s="3" t="inlineStr">
@@ -18797,7 +18859,7 @@
       </c>
     </row>
     <row r="403" ht="17" customHeight="1">
-      <c r="A403" s="8" t="n">
+      <c r="A403" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B403" s="9" t="inlineStr">
@@ -18828,7 +18890,7 @@
       </c>
     </row>
     <row r="404" ht="17" customHeight="1">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B404" s="3" t="inlineStr">
@@ -18859,7 +18921,7 @@
       </c>
     </row>
     <row r="405" ht="17" customHeight="1">
-      <c r="A405" s="8" t="n">
+      <c r="A405" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B405" s="9" t="inlineStr">
@@ -18890,7 +18952,7 @@
       </c>
     </row>
     <row r="406" ht="17" customHeight="1">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B406" s="3" t="inlineStr">
@@ -18921,7 +18983,7 @@
       </c>
     </row>
     <row r="407" ht="17" customHeight="1">
-      <c r="A407" s="8" t="n">
+      <c r="A407" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B407" s="9" t="inlineStr">
@@ -18952,7 +19014,7 @@
       </c>
     </row>
     <row r="408" ht="17" customHeight="1">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B408" s="3" t="inlineStr">
@@ -18983,7 +19045,7 @@
       </c>
     </row>
     <row r="409" ht="17" customHeight="1">
-      <c r="A409" s="8" t="n">
+      <c r="A409" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B409" s="9" t="inlineStr">
@@ -19014,7 +19076,7 @@
       </c>
     </row>
     <row r="410" ht="17" customHeight="1">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B410" s="3" t="inlineStr">
@@ -19045,7 +19107,7 @@
       </c>
     </row>
     <row r="411" ht="17" customHeight="1">
-      <c r="A411" s="8" t="n">
+      <c r="A411" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B411" s="9" t="inlineStr">
@@ -19076,7 +19138,7 @@
       </c>
     </row>
     <row r="412" ht="17" customHeight="1">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B412" s="3" t="inlineStr">
@@ -19107,7 +19169,7 @@
       </c>
     </row>
     <row r="413" ht="17" customHeight="1">
-      <c r="A413" s="8" t="n">
+      <c r="A413" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B413" s="9" t="inlineStr">
@@ -19138,7 +19200,7 @@
       </c>
     </row>
     <row r="414" ht="17" customHeight="1">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B414" s="3" t="inlineStr">
@@ -19169,7 +19231,7 @@
       </c>
     </row>
     <row r="415" ht="17" customHeight="1">
-      <c r="A415" s="8" t="n">
+      <c r="A415" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B415" s="9" t="inlineStr">
@@ -19200,7 +19262,7 @@
       </c>
     </row>
     <row r="416" ht="17" customHeight="1">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B416" s="3" t="inlineStr">
@@ -19231,7 +19293,7 @@
       </c>
     </row>
     <row r="417" ht="17" customHeight="1">
-      <c r="A417" s="8" t="n">
+      <c r="A417" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B417" s="9" t="inlineStr">
@@ -19262,7 +19324,7 @@
       </c>
     </row>
     <row r="418" ht="17" customHeight="1">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -19293,7 +19355,7 @@
       </c>
     </row>
     <row r="419" ht="17" customHeight="1">
-      <c r="A419" s="8" t="n">
+      <c r="A419" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B419" s="9" t="inlineStr">
@@ -19324,7 +19386,7 @@
       </c>
     </row>
     <row r="420" ht="17" customHeight="1">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B420" s="3" t="inlineStr">
@@ -19355,7 +19417,7 @@
       </c>
     </row>
     <row r="421" ht="17" customHeight="1">
-      <c r="A421" s="8" t="n">
+      <c r="A421" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B421" s="9" t="inlineStr">
@@ -19386,7 +19448,7 @@
       </c>
     </row>
     <row r="422" ht="17" customHeight="1">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B422" s="3" t="inlineStr">
@@ -19417,7 +19479,7 @@
       </c>
     </row>
     <row r="423" ht="17" customHeight="1">
-      <c r="A423" s="8" t="n">
+      <c r="A423" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B423" s="9" t="inlineStr">
@@ -19448,7 +19510,7 @@
       </c>
     </row>
     <row r="424" ht="17" customHeight="1">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B424" s="3" t="inlineStr">
@@ -19479,7 +19541,7 @@
       </c>
     </row>
     <row r="425" ht="17" customHeight="1">
-      <c r="A425" s="8" t="n">
+      <c r="A425" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B425" s="9" t="inlineStr">
@@ -19510,7 +19572,7 @@
       </c>
     </row>
     <row r="426" ht="17" customHeight="1">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B426" s="3" t="inlineStr">
@@ -19541,7 +19603,7 @@
       </c>
     </row>
     <row r="427" ht="17" customHeight="1">
-      <c r="A427" s="8" t="n">
+      <c r="A427" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B427" s="9" t="inlineStr">
@@ -19572,7 +19634,7 @@
       </c>
     </row>
     <row r="428" ht="17" customHeight="1">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B428" s="3" t="inlineStr">
@@ -19603,7 +19665,7 @@
       </c>
     </row>
     <row r="429" ht="17" customHeight="1">
-      <c r="A429" s="8" t="n">
+      <c r="A429" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B429" s="9" t="inlineStr">
@@ -19634,7 +19696,7 @@
       </c>
     </row>
     <row r="430" ht="17" customHeight="1">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B430" s="3" t="inlineStr">
@@ -19665,7 +19727,7 @@
       </c>
     </row>
     <row r="431" ht="17" customHeight="1">
-      <c r="A431" s="8" t="n">
+      <c r="A431" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B431" s="9" t="inlineStr">
@@ -19696,7 +19758,7 @@
       </c>
     </row>
     <row r="432" ht="17" customHeight="1">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B432" s="3" t="inlineStr">
@@ -19727,7 +19789,7 @@
       </c>
     </row>
     <row r="433" ht="17" customHeight="1">
-      <c r="A433" s="8" t="n">
+      <c r="A433" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B433" s="9" t="inlineStr">
@@ -19758,7 +19820,7 @@
       </c>
     </row>
     <row r="434" ht="17" customHeight="1">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B434" s="3" t="inlineStr">
@@ -19789,7 +19851,7 @@
       </c>
     </row>
     <row r="435" ht="17" customHeight="1">
-      <c r="A435" s="8" t="n">
+      <c r="A435" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B435" s="9" t="inlineStr">
@@ -19820,7 +19882,7 @@
       </c>
     </row>
     <row r="436" ht="17" customHeight="1">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B436" s="3" t="inlineStr">
@@ -19851,7 +19913,7 @@
       </c>
     </row>
     <row r="437" ht="17" customHeight="1">
-      <c r="A437" s="8" t="n">
+      <c r="A437" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B437" s="9" t="inlineStr">
@@ -19882,7 +19944,7 @@
       </c>
     </row>
     <row r="438" ht="17" customHeight="1">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B438" s="3" t="inlineStr">
@@ -19913,7 +19975,7 @@
       </c>
     </row>
     <row r="439" ht="17" customHeight="1">
-      <c r="A439" s="8" t="n">
+      <c r="A439" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B439" s="9" t="inlineStr">
@@ -19944,7 +20006,7 @@
       </c>
     </row>
     <row r="440" ht="17" customHeight="1">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -19975,7 +20037,7 @@
       </c>
     </row>
     <row r="441" ht="17" customHeight="1">
-      <c r="A441" s="8" t="n">
+      <c r="A441" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B441" s="9" t="inlineStr">
@@ -20006,7 +20068,7 @@
       </c>
     </row>
     <row r="442" ht="17" customHeight="1">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -20037,7 +20099,7 @@
       </c>
     </row>
     <row r="443" ht="17" customHeight="1">
-      <c r="A443" s="8" t="n">
+      <c r="A443" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -20068,7 +20130,7 @@
       </c>
     </row>
     <row r="444" ht="17" customHeight="1">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B444" s="3" t="inlineStr">
@@ -20099,7 +20161,7 @@
       </c>
     </row>
     <row r="445" ht="17" customHeight="1">
-      <c r="A445" s="8" t="n">
+      <c r="A445" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B445" s="9" t="inlineStr">
@@ -20130,7 +20192,7 @@
       </c>
     </row>
     <row r="446" ht="17" customHeight="1">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B446" s="3" t="inlineStr">
@@ -20161,7 +20223,7 @@
       </c>
     </row>
     <row r="447" ht="17" customHeight="1">
-      <c r="A447" s="8" t="n">
+      <c r="A447" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B447" s="9" t="inlineStr">
@@ -20192,7 +20254,7 @@
       </c>
     </row>
     <row r="448" ht="17" customHeight="1">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B448" s="3" t="inlineStr">
@@ -20223,7 +20285,7 @@
       </c>
     </row>
     <row r="449" ht="17" customHeight="1">
-      <c r="A449" s="8" t="n">
+      <c r="A449" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B449" s="9" t="inlineStr">
@@ -20254,7 +20316,7 @@
       </c>
     </row>
     <row r="450" ht="17" customHeight="1">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B450" s="3" t="inlineStr">
@@ -20285,7 +20347,7 @@
       </c>
     </row>
     <row r="451" ht="17" customHeight="1">
-      <c r="A451" s="8" t="n">
+      <c r="A451" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B451" s="9" t="inlineStr">
@@ -20316,7 +20378,7 @@
       </c>
     </row>
     <row r="452" ht="17" customHeight="1">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B452" s="3" t="inlineStr">
@@ -20347,7 +20409,7 @@
       </c>
     </row>
     <row r="453" ht="17" customHeight="1">
-      <c r="A453" s="8" t="n">
+      <c r="A453" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B453" s="9" t="inlineStr">
@@ -20378,7 +20440,7 @@
       </c>
     </row>
     <row r="454" ht="17" customHeight="1">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B454" s="3" t="inlineStr">
@@ -20409,7 +20471,7 @@
       </c>
     </row>
     <row r="455" ht="17" customHeight="1">
-      <c r="A455" s="8" t="n">
+      <c r="A455" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B455" s="9" t="inlineStr">
@@ -20440,7 +20502,7 @@
       </c>
     </row>
     <row r="456" ht="17" customHeight="1">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B456" s="3" t="inlineStr">
@@ -20471,7 +20533,7 @@
       </c>
     </row>
     <row r="457" ht="17" customHeight="1">
-      <c r="A457" s="8" t="n">
+      <c r="A457" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B457" s="9" t="inlineStr">
@@ -20502,7 +20564,7 @@
       </c>
     </row>
     <row r="458" ht="17" customHeight="1">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B458" s="3" t="inlineStr">
@@ -20533,7 +20595,7 @@
       </c>
     </row>
     <row r="459" ht="17" customHeight="1">
-      <c r="A459" s="8" t="n">
+      <c r="A459" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B459" s="9" t="inlineStr">
@@ -20564,7 +20626,7 @@
       </c>
     </row>
     <row r="460" ht="17" customHeight="1">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B460" s="3" t="inlineStr">
@@ -20595,7 +20657,7 @@
       </c>
     </row>
     <row r="461" ht="17" customHeight="1">
-      <c r="A461" s="8" t="n">
+      <c r="A461" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B461" s="9" t="inlineStr">
@@ -20626,7 +20688,7 @@
       </c>
     </row>
     <row r="462" ht="17" customHeight="1">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B462" s="3" t="inlineStr">
@@ -20657,7 +20719,7 @@
       </c>
     </row>
     <row r="463" ht="17" customHeight="1">
-      <c r="A463" s="8" t="n">
+      <c r="A463" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B463" s="9" t="inlineStr">
@@ -20688,7 +20750,7 @@
       </c>
     </row>
     <row r="464" ht="17" customHeight="1">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B464" s="3" t="inlineStr">
@@ -20719,7 +20781,7 @@
       </c>
     </row>
     <row r="465" ht="17" customHeight="1">
-      <c r="A465" s="8" t="n">
+      <c r="A465" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B465" s="9" t="inlineStr">
@@ -20750,7 +20812,7 @@
       </c>
     </row>
     <row r="466" ht="17" customHeight="1">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B466" s="3" t="inlineStr">
@@ -20781,7 +20843,7 @@
       </c>
     </row>
     <row r="467" ht="17" customHeight="1">
-      <c r="A467" s="8" t="n">
+      <c r="A467" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B467" s="9" t="inlineStr">
@@ -20812,7 +20874,7 @@
       </c>
     </row>
     <row r="468" ht="17" customHeight="1">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B468" s="3" t="inlineStr">
@@ -20843,7 +20905,7 @@
       </c>
     </row>
     <row r="469" ht="17" customHeight="1">
-      <c r="A469" s="8" t="n">
+      <c r="A469" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B469" s="9" t="inlineStr">
@@ -20874,7 +20936,7 @@
       </c>
     </row>
     <row r="470" ht="17" customHeight="1">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B470" s="3" t="inlineStr">
@@ -20905,7 +20967,7 @@
       </c>
     </row>
     <row r="471" ht="17" customHeight="1">
-      <c r="A471" s="8" t="n">
+      <c r="A471" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B471" s="9" t="inlineStr">
@@ -20936,7 +20998,7 @@
       </c>
     </row>
     <row r="472" ht="17" customHeight="1">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B472" s="3" t="inlineStr">
@@ -20967,7 +21029,7 @@
       </c>
     </row>
     <row r="473" ht="17" customHeight="1">
-      <c r="A473" s="8" t="n">
+      <c r="A473" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B473" s="9" t="inlineStr">
@@ -20998,7 +21060,7 @@
       </c>
     </row>
     <row r="474" ht="17" customHeight="1">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B474" s="3" t="inlineStr">
@@ -21029,7 +21091,7 @@
       </c>
     </row>
     <row r="475" ht="17" customHeight="1">
-      <c r="A475" s="8" t="n">
+      <c r="A475" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B475" s="9" t="inlineStr">
@@ -21060,7 +21122,7 @@
       </c>
     </row>
     <row r="476" ht="17" customHeight="1">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B476" s="3" t="inlineStr">
@@ -21091,7 +21153,7 @@
       </c>
     </row>
     <row r="477" ht="17" customHeight="1">
-      <c r="A477" s="8" t="n">
+      <c r="A477" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B477" s="9" t="inlineStr">
@@ -21122,7 +21184,7 @@
       </c>
     </row>
     <row r="478" ht="17" customHeight="1">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B478" s="3" t="inlineStr">
@@ -21153,7 +21215,7 @@
       </c>
     </row>
     <row r="479" ht="17" customHeight="1">
-      <c r="A479" s="8" t="n">
+      <c r="A479" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B479" s="9" t="inlineStr">
@@ -21184,7 +21246,7 @@
       </c>
     </row>
     <row r="480" ht="17" customHeight="1">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B480" s="3" t="inlineStr">
@@ -21215,7 +21277,7 @@
       </c>
     </row>
     <row r="481" ht="17" customHeight="1">
-      <c r="A481" s="8" t="n">
+      <c r="A481" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B481" s="9" t="inlineStr">
@@ -21246,7 +21308,7 @@
       </c>
     </row>
     <row r="482" ht="17" customHeight="1">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B482" s="3" t="inlineStr">
@@ -21277,7 +21339,7 @@
       </c>
     </row>
     <row r="483" ht="17" customHeight="1">
-      <c r="A483" s="8" t="n">
+      <c r="A483" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B483" s="9" t="inlineStr">
@@ -21308,7 +21370,7 @@
       </c>
     </row>
     <row r="484" ht="17" customHeight="1">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B484" s="3" t="inlineStr">
@@ -21339,7 +21401,7 @@
       </c>
     </row>
     <row r="485" ht="17" customHeight="1">
-      <c r="A485" s="8" t="n">
+      <c r="A485" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B485" s="9" t="inlineStr">
@@ -21370,7 +21432,7 @@
       </c>
     </row>
     <row r="486" ht="17" customHeight="1">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B486" s="3" t="inlineStr">
@@ -21401,7 +21463,7 @@
       </c>
     </row>
     <row r="487" ht="17" customHeight="1">
-      <c r="A487" s="8" t="n">
+      <c r="A487" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B487" s="9" t="inlineStr">
@@ -21432,7 +21494,7 @@
       </c>
     </row>
     <row r="488" ht="17" customHeight="1">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B488" s="3" t="inlineStr">
@@ -21463,7 +21525,7 @@
       </c>
     </row>
     <row r="489" ht="17" customHeight="1">
-      <c r="A489" s="8" t="n">
+      <c r="A489" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B489" s="9" t="inlineStr">
@@ -21494,7 +21556,7 @@
       </c>
     </row>
     <row r="490" ht="17" customHeight="1">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B490" s="3" t="inlineStr">
@@ -21525,7 +21587,7 @@
       </c>
     </row>
     <row r="491" ht="17" customHeight="1">
-      <c r="A491" s="8" t="n">
+      <c r="A491" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B491" s="9" t="inlineStr">
@@ -21556,7 +21618,7 @@
       </c>
     </row>
     <row r="492" ht="17" customHeight="1">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B492" s="3" t="inlineStr">
@@ -21587,7 +21649,7 @@
       </c>
     </row>
     <row r="493" ht="17" customHeight="1">
-      <c r="A493" s="8" t="n">
+      <c r="A493" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B493" s="9" t="inlineStr">
@@ -21618,7 +21680,7 @@
       </c>
     </row>
     <row r="494" ht="17" customHeight="1">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B494" s="3" t="inlineStr">
@@ -21649,7 +21711,7 @@
       </c>
     </row>
     <row r="495" ht="17" customHeight="1">
-      <c r="A495" s="8" t="n">
+      <c r="A495" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B495" s="9" t="inlineStr">
@@ -21680,7 +21742,7 @@
       </c>
     </row>
     <row r="496" ht="17" customHeight="1">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B496" s="3" t="inlineStr">
@@ -21711,7 +21773,7 @@
       </c>
     </row>
     <row r="497" ht="17" customHeight="1">
-      <c r="A497" s="8" t="n">
+      <c r="A497" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B497" s="9" t="inlineStr">
@@ -21742,7 +21804,7 @@
       </c>
     </row>
     <row r="498" ht="17" customHeight="1">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B498" s="3" t="inlineStr">
@@ -21773,7 +21835,7 @@
       </c>
     </row>
     <row r="499" ht="17" customHeight="1">
-      <c r="A499" s="8" t="n">
+      <c r="A499" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B499" s="9" t="inlineStr">
@@ -21804,7 +21866,7 @@
       </c>
     </row>
     <row r="500" ht="17" customHeight="1">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B500" s="3" t="inlineStr">
@@ -21835,7 +21897,7 @@
       </c>
     </row>
     <row r="501" ht="17" customHeight="1">
-      <c r="A501" s="8" t="n">
+      <c r="A501" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B501" s="9" t="inlineStr">
@@ -21866,7 +21928,7 @@
       </c>
     </row>
     <row r="502" ht="17" customHeight="1">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B502" s="3" t="inlineStr">
@@ -21897,7 +21959,7 @@
       </c>
     </row>
     <row r="503" ht="17" customHeight="1">
-      <c r="A503" s="8" t="n">
+      <c r="A503" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B503" s="9" t="inlineStr">
@@ -21928,7 +21990,7 @@
       </c>
     </row>
     <row r="504" ht="17" customHeight="1">
-      <c r="A504" s="2" t="n">
+      <c r="A504" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B504" s="3" t="inlineStr">
@@ -21959,7 +22021,7 @@
       </c>
     </row>
     <row r="505" ht="17" customHeight="1">
-      <c r="A505" s="8" t="n">
+      <c r="A505" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B505" s="9" t="inlineStr">
@@ -21990,7 +22052,7 @@
       </c>
     </row>
     <row r="506" ht="17" customHeight="1">
-      <c r="A506" s="2" t="n">
+      <c r="A506" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B506" s="3" t="inlineStr">
@@ -22021,7 +22083,7 @@
       </c>
     </row>
     <row r="507" ht="17" customHeight="1">
-      <c r="A507" s="8" t="n">
+      <c r="A507" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B507" s="9" t="inlineStr">
@@ -22052,7 +22114,7 @@
       </c>
     </row>
     <row r="508" ht="17" customHeight="1">
-      <c r="A508" s="2" t="n">
+      <c r="A508" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B508" s="3" t="inlineStr">
@@ -22083,7 +22145,7 @@
       </c>
     </row>
     <row r="509" ht="17" customHeight="1">
-      <c r="A509" s="8" t="n">
+      <c r="A509" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B509" s="9" t="inlineStr">
@@ -22114,7 +22176,7 @@
       </c>
     </row>
     <row r="510" ht="17" customHeight="1">
-      <c r="A510" s="2" t="n">
+      <c r="A510" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B510" s="3" t="inlineStr">
@@ -22145,7 +22207,7 @@
       </c>
     </row>
     <row r="511" ht="17" customHeight="1">
-      <c r="A511" s="8" t="n">
+      <c r="A511" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B511" s="9" t="inlineStr">
@@ -22176,7 +22238,7 @@
       </c>
     </row>
     <row r="512" ht="17" customHeight="1">
-      <c r="A512" s="2" t="n">
+      <c r="A512" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B512" s="3" t="inlineStr">
@@ -22207,7 +22269,7 @@
       </c>
     </row>
     <row r="513" ht="17" customHeight="1">
-      <c r="A513" s="8" t="n">
+      <c r="A513" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B513" s="9" t="inlineStr">
@@ -22238,7 +22300,7 @@
       </c>
     </row>
     <row r="514" ht="17" customHeight="1">
-      <c r="A514" s="2" t="n">
+      <c r="A514" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B514" s="3" t="inlineStr">
@@ -22269,7 +22331,7 @@
       </c>
     </row>
     <row r="515" ht="17" customHeight="1">
-      <c r="A515" s="8" t="n">
+      <c r="A515" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B515" s="9" t="inlineStr">
@@ -22300,7 +22362,7 @@
       </c>
     </row>
     <row r="516" ht="17" customHeight="1">
-      <c r="A516" s="2" t="n">
+      <c r="A516" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B516" s="3" t="inlineStr">
@@ -22331,7 +22393,7 @@
       </c>
     </row>
     <row r="517" ht="17" customHeight="1">
-      <c r="A517" s="8" t="n">
+      <c r="A517" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B517" s="9" t="inlineStr">
@@ -22362,7 +22424,7 @@
       </c>
     </row>
     <row r="518" ht="17" customHeight="1">
-      <c r="A518" s="2" t="n">
+      <c r="A518" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B518" s="3" t="inlineStr">
@@ -22393,7 +22455,7 @@
       </c>
     </row>
     <row r="519" ht="17" customHeight="1">
-      <c r="A519" s="8" t="n">
+      <c r="A519" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B519" s="9" t="inlineStr">
@@ -22424,7 +22486,7 @@
       </c>
     </row>
     <row r="520" ht="17" customHeight="1">
-      <c r="A520" s="2" t="n">
+      <c r="A520" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B520" s="3" t="inlineStr">
@@ -22455,7 +22517,7 @@
       </c>
     </row>
     <row r="521" ht="17" customHeight="1">
-      <c r="A521" s="8" t="n">
+      <c r="A521" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B521" s="9" t="inlineStr">
@@ -22486,7 +22548,7 @@
       </c>
     </row>
     <row r="522" ht="17" customHeight="1">
-      <c r="A522" s="2" t="n">
+      <c r="A522" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B522" s="3" t="inlineStr">
@@ -22517,7 +22579,7 @@
       </c>
     </row>
     <row r="523" ht="17" customHeight="1">
-      <c r="A523" s="8" t="n">
+      <c r="A523" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B523" s="9" t="inlineStr">
@@ -22548,7 +22610,7 @@
       </c>
     </row>
     <row r="524" ht="17" customHeight="1">
-      <c r="A524" s="2" t="n">
+      <c r="A524" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B524" s="3" t="inlineStr">
@@ -22579,7 +22641,7 @@
       </c>
     </row>
     <row r="525" ht="17" customHeight="1">
-      <c r="A525" s="8" t="n">
+      <c r="A525" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B525" s="9" t="inlineStr">
@@ -22610,7 +22672,7 @@
       </c>
     </row>
     <row r="526" ht="17" customHeight="1">
-      <c r="A526" s="2" t="n">
+      <c r="A526" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B526" s="3" t="inlineStr">
@@ -22641,7 +22703,7 @@
       </c>
     </row>
     <row r="527" ht="17" customHeight="1">
-      <c r="A527" s="8" t="n">
+      <c r="A527" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B527" s="9" t="inlineStr">
@@ -22672,7 +22734,7 @@
       </c>
     </row>
     <row r="528" ht="17" customHeight="1">
-      <c r="A528" s="2" t="n">
+      <c r="A528" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B528" s="3" t="inlineStr">
@@ -22703,7 +22765,7 @@
       </c>
     </row>
     <row r="529" ht="17" customHeight="1">
-      <c r="A529" s="8" t="n">
+      <c r="A529" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B529" s="9" t="inlineStr">
@@ -22734,7 +22796,7 @@
       </c>
     </row>
     <row r="530" ht="17" customHeight="1">
-      <c r="A530" s="2" t="n">
+      <c r="A530" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B530" s="3" t="inlineStr">
@@ -22765,7 +22827,7 @@
       </c>
     </row>
     <row r="531" ht="17" customHeight="1">
-      <c r="A531" s="8" t="n">
+      <c r="A531" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B531" s="9" t="inlineStr">
@@ -22796,7 +22858,7 @@
       </c>
     </row>
     <row r="532" ht="17" customHeight="1">
-      <c r="A532" s="2" t="n">
+      <c r="A532" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B532" s="3" t="inlineStr">
@@ -22827,7 +22889,7 @@
       </c>
     </row>
     <row r="533" ht="17" customHeight="1">
-      <c r="A533" s="8" t="n">
+      <c r="A533" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B533" s="9" t="inlineStr">
@@ -22858,7 +22920,7 @@
       </c>
     </row>
     <row r="534" ht="17" customHeight="1">
-      <c r="A534" s="2" t="n">
+      <c r="A534" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B534" s="3" t="inlineStr">
@@ -22889,7 +22951,7 @@
       </c>
     </row>
     <row r="535" ht="17" customHeight="1">
-      <c r="A535" s="8" t="n">
+      <c r="A535" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B535" s="9" t="inlineStr">
@@ -22920,7 +22982,7 @@
       </c>
     </row>
     <row r="536" ht="17" customHeight="1">
-      <c r="A536" s="2" t="n">
+      <c r="A536" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B536" s="3" t="inlineStr">
@@ -22951,7 +23013,7 @@
       </c>
     </row>
     <row r="537" ht="17" customHeight="1">
-      <c r="A537" s="8" t="n">
+      <c r="A537" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B537" s="9" t="inlineStr">
@@ -22982,7 +23044,7 @@
       </c>
     </row>
     <row r="538" ht="17" customHeight="1">
-      <c r="A538" s="2" t="n">
+      <c r="A538" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B538" s="3" t="inlineStr">
@@ -23013,7 +23075,7 @@
       </c>
     </row>
     <row r="539" ht="17" customHeight="1">
-      <c r="A539" s="8" t="n">
+      <c r="A539" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B539" s="9" t="inlineStr">
@@ -23044,7 +23106,7 @@
       </c>
     </row>
     <row r="540" ht="17" customHeight="1">
-      <c r="A540" s="2" t="n">
+      <c r="A540" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B540" s="3" t="inlineStr">
@@ -23075,7 +23137,7 @@
       </c>
     </row>
     <row r="541" ht="17" customHeight="1">
-      <c r="A541" s="8" t="n">
+      <c r="A541" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B541" s="9" t="inlineStr">
@@ -23106,7 +23168,7 @@
       </c>
     </row>
     <row r="542" ht="17" customHeight="1">
-      <c r="A542" s="2" t="n">
+      <c r="A542" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B542" s="3" t="inlineStr">
@@ -23137,7 +23199,7 @@
       </c>
     </row>
     <row r="543" ht="17" customHeight="1">
-      <c r="A543" s="8" t="n">
+      <c r="A543" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B543" s="9" t="inlineStr">
@@ -23168,7 +23230,7 @@
       </c>
     </row>
     <row r="544" ht="17" customHeight="1">
-      <c r="A544" s="2" t="n">
+      <c r="A544" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B544" s="3" t="inlineStr">
@@ -23199,7 +23261,7 @@
       </c>
     </row>
     <row r="545" ht="17" customHeight="1">
-      <c r="A545" s="8" t="n">
+      <c r="A545" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B545" s="9" t="inlineStr">
@@ -23230,7 +23292,7 @@
       </c>
     </row>
     <row r="546" ht="17" customHeight="1">
-      <c r="A546" s="2" t="n">
+      <c r="A546" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B546" s="3" t="inlineStr">
@@ -23261,7 +23323,7 @@
       </c>
     </row>
     <row r="547" ht="17" customHeight="1">
-      <c r="A547" s="8" t="n">
+      <c r="A547" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B547" s="9" t="inlineStr">
@@ -23292,7 +23354,7 @@
       </c>
     </row>
     <row r="548" ht="17" customHeight="1">
-      <c r="A548" s="2" t="n">
+      <c r="A548" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B548" s="3" t="inlineStr">
@@ -23323,7 +23385,7 @@
       </c>
     </row>
     <row r="549" ht="17" customHeight="1">
-      <c r="A549" s="8" t="n">
+      <c r="A549" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B549" s="9" t="inlineStr">
@@ -23354,7 +23416,7 @@
       </c>
     </row>
     <row r="550" ht="17" customHeight="1">
-      <c r="A550" s="2" t="n">
+      <c r="A550" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B550" s="3" t="inlineStr">
@@ -23385,7 +23447,7 @@
       </c>
     </row>
     <row r="551" ht="17" customHeight="1">
-      <c r="A551" s="8" t="n">
+      <c r="A551" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B551" s="9" t="inlineStr">
@@ -23416,7 +23478,7 @@
       </c>
     </row>
     <row r="552" ht="17" customHeight="1">
-      <c r="A552" s="2" t="n">
+      <c r="A552" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B552" s="3" t="inlineStr">
@@ -23447,7 +23509,7 @@
       </c>
     </row>
     <row r="553" ht="17" customHeight="1">
-      <c r="A553" s="8" t="n">
+      <c r="A553" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B553" s="9" t="inlineStr">
@@ -23478,7 +23540,7 @@
       </c>
     </row>
     <row r="554" ht="17" customHeight="1">
-      <c r="A554" s="2" t="n">
+      <c r="A554" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B554" s="3" t="inlineStr">
@@ -23509,7 +23571,7 @@
       </c>
     </row>
     <row r="555" ht="17" customHeight="1">
-      <c r="A555" s="8" t="n">
+      <c r="A555" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B555" s="9" t="inlineStr">
@@ -23540,7 +23602,7 @@
       </c>
     </row>
     <row r="556" ht="17" customHeight="1">
-      <c r="A556" s="2" t="n">
+      <c r="A556" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B556" s="3" t="inlineStr">
@@ -23571,7 +23633,7 @@
       </c>
     </row>
     <row r="557" ht="17" customHeight="1">
-      <c r="A557" s="8" t="n">
+      <c r="A557" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B557" s="9" t="inlineStr">
@@ -23602,7 +23664,7 @@
       </c>
     </row>
     <row r="558" ht="17" customHeight="1">
-      <c r="A558" s="2" t="n">
+      <c r="A558" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B558" s="3" t="inlineStr">
@@ -23633,7 +23695,7 @@
       </c>
     </row>
     <row r="559" ht="17" customHeight="1">
-      <c r="A559" s="8" t="n">
+      <c r="A559" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B559" s="9" t="inlineStr">
@@ -23664,7 +23726,7 @@
       </c>
     </row>
     <row r="560" ht="17" customHeight="1">
-      <c r="A560" s="2" t="n">
+      <c r="A560" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B560" s="3" t="inlineStr">
@@ -23695,7 +23757,7 @@
       </c>
     </row>
     <row r="561" ht="17" customHeight="1">
-      <c r="A561" s="8" t="n">
+      <c r="A561" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B561" s="9" t="inlineStr">
@@ -23726,7 +23788,7 @@
       </c>
     </row>
     <row r="562" ht="17" customHeight="1">
-      <c r="A562" s="2" t="n">
+      <c r="A562" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B562" s="3" t="inlineStr">
@@ -23757,7 +23819,7 @@
       </c>
     </row>
     <row r="563" ht="17" customHeight="1">
-      <c r="A563" s="8" t="n">
+      <c r="A563" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B563" s="9" t="inlineStr">
@@ -23788,7 +23850,7 @@
       </c>
     </row>
     <row r="564" ht="17" customHeight="1">
-      <c r="A564" s="2" t="n">
+      <c r="A564" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B564" s="3" t="inlineStr">
@@ -23819,7 +23881,7 @@
       </c>
     </row>
     <row r="565" ht="17" customHeight="1">
-      <c r="A565" s="8" t="n">
+      <c r="A565" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B565" s="9" t="inlineStr">
@@ -23850,7 +23912,7 @@
       </c>
     </row>
     <row r="566" ht="17" customHeight="1">
-      <c r="A566" s="2" t="n">
+      <c r="A566" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B566" s="3" t="inlineStr">
@@ -23881,7 +23943,7 @@
       </c>
     </row>
     <row r="567" ht="17" customHeight="1">
-      <c r="A567" s="8" t="n">
+      <c r="A567" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B567" s="9" t="inlineStr">
@@ -23912,7 +23974,7 @@
       </c>
     </row>
     <row r="568" ht="17" customHeight="1">
-      <c r="A568" s="2" t="n">
+      <c r="A568" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B568" s="3" t="inlineStr">
@@ -23943,7 +24005,7 @@
       </c>
     </row>
     <row r="569" ht="17" customHeight="1">
-      <c r="A569" s="8" t="n">
+      <c r="A569" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B569" s="9" t="inlineStr">
@@ -23974,7 +24036,7 @@
       </c>
     </row>
     <row r="570" ht="17" customHeight="1">
-      <c r="A570" s="2" t="n">
+      <c r="A570" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B570" s="3" t="inlineStr">
@@ -24005,7 +24067,7 @@
       </c>
     </row>
     <row r="571" ht="17" customHeight="1">
-      <c r="A571" s="8" t="n">
+      <c r="A571" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B571" s="9" t="inlineStr">
@@ -24036,7 +24098,7 @@
       </c>
     </row>
     <row r="572" ht="17" customHeight="1">
-      <c r="A572" s="2" t="n">
+      <c r="A572" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B572" s="3" t="inlineStr">
@@ -24067,7 +24129,7 @@
       </c>
     </row>
     <row r="573" ht="17" customHeight="1">
-      <c r="A573" s="8" t="n">
+      <c r="A573" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B573" s="9" t="inlineStr">
@@ -24098,7 +24160,7 @@
       </c>
     </row>
     <row r="574" ht="17" customHeight="1">
-      <c r="A574" s="2" t="n">
+      <c r="A574" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B574" s="3" t="inlineStr">
@@ -24129,7 +24191,7 @@
       </c>
     </row>
     <row r="575" ht="17" customHeight="1">
-      <c r="A575" s="8" t="n">
+      <c r="A575" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B575" s="9" t="inlineStr">
@@ -24160,7 +24222,7 @@
       </c>
     </row>
     <row r="576" ht="17" customHeight="1">
-      <c r="A576" s="2" t="n">
+      <c r="A576" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B576" s="3" t="inlineStr">
@@ -24191,7 +24253,7 @@
       </c>
     </row>
     <row r="577" ht="17" customHeight="1">
-      <c r="A577" s="8" t="n">
+      <c r="A577" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B577" s="9" t="inlineStr">
@@ -24222,7 +24284,7 @@
       </c>
     </row>
     <row r="578" ht="17" customHeight="1">
-      <c r="A578" s="2" t="n">
+      <c r="A578" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B578" s="3" t="inlineStr">
@@ -24253,7 +24315,7 @@
       </c>
     </row>
     <row r="579" ht="17" customHeight="1">
-      <c r="A579" s="8" t="n">
+      <c r="A579" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B579" s="9" t="inlineStr">
@@ -24284,7 +24346,7 @@
       </c>
     </row>
     <row r="580" ht="17" customHeight="1">
-      <c r="A580" s="2" t="n">
+      <c r="A580" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B580" s="3" t="inlineStr">
@@ -24315,7 +24377,7 @@
       </c>
     </row>
     <row r="581" ht="17" customHeight="1">
-      <c r="A581" s="8" t="n">
+      <c r="A581" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B581" s="9" t="inlineStr">
@@ -24346,7 +24408,7 @@
       </c>
     </row>
     <row r="582" ht="17" customHeight="1">
-      <c r="A582" s="2" t="n">
+      <c r="A582" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B582" s="3" t="inlineStr">
@@ -24377,7 +24439,7 @@
       </c>
     </row>
     <row r="583" ht="17" customHeight="1">
-      <c r="A583" s="8" t="n">
+      <c r="A583" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B583" s="9" t="inlineStr">
@@ -24408,7 +24470,7 @@
       </c>
     </row>
     <row r="584" ht="17" customHeight="1">
-      <c r="A584" s="2" t="n">
+      <c r="A584" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B584" s="3" t="inlineStr">
@@ -24439,7 +24501,7 @@
       </c>
     </row>
     <row r="585" ht="17" customHeight="1">
-      <c r="A585" s="8" t="n">
+      <c r="A585" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B585" s="9" t="inlineStr">
@@ -24470,7 +24532,7 @@
       </c>
     </row>
     <row r="586" ht="17" customHeight="1">
-      <c r="A586" s="2" t="n">
+      <c r="A586" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B586" s="3" t="inlineStr">
@@ -24501,7 +24563,7 @@
       </c>
     </row>
     <row r="587" ht="17" customHeight="1">
-      <c r="A587" s="8" t="n">
+      <c r="A587" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B587" s="9" t="inlineStr">
@@ -24532,7 +24594,7 @@
       </c>
     </row>
     <row r="588" ht="17" customHeight="1">
-      <c r="A588" s="2" t="n">
+      <c r="A588" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B588" s="3" t="inlineStr">
@@ -24563,7 +24625,7 @@
       </c>
     </row>
     <row r="589" ht="17" customHeight="1">
-      <c r="A589" s="8" t="n">
+      <c r="A589" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B589" s="9" t="inlineStr">
@@ -24594,7 +24656,7 @@
       </c>
     </row>
     <row r="590" ht="17" customHeight="1">
-      <c r="A590" s="2" t="n">
+      <c r="A590" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B590" s="3" t="inlineStr">
@@ -24625,7 +24687,7 @@
       </c>
     </row>
     <row r="591" ht="17" customHeight="1">
-      <c r="A591" s="8" t="n">
+      <c r="A591" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B591" s="9" t="inlineStr">
@@ -24656,7 +24718,7 @@
       </c>
     </row>
     <row r="592" ht="17" customHeight="1">
-      <c r="A592" s="2" t="n">
+      <c r="A592" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B592" s="3" t="inlineStr">
@@ -24687,7 +24749,7 @@
       </c>
     </row>
     <row r="593" ht="17" customHeight="1">
-      <c r="A593" s="8" t="n">
+      <c r="A593" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B593" s="9" t="inlineStr">
@@ -24718,7 +24780,7 @@
       </c>
     </row>
     <row r="594" ht="17" customHeight="1">
-      <c r="A594" s="2" t="n">
+      <c r="A594" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B594" s="3" t="inlineStr">
@@ -24749,7 +24811,7 @@
       </c>
     </row>
     <row r="595" ht="17" customHeight="1">
-      <c r="A595" s="8" t="n">
+      <c r="A595" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B595" s="9" t="inlineStr">
@@ -24780,7 +24842,7 @@
       </c>
     </row>
     <row r="596" ht="17" customHeight="1">
-      <c r="A596" s="2" t="n">
+      <c r="A596" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B596" s="3" t="inlineStr">
@@ -24811,7 +24873,7 @@
       </c>
     </row>
     <row r="597" ht="17" customHeight="1">
-      <c r="A597" s="8" t="n">
+      <c r="A597" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B597" s="9" t="inlineStr">
@@ -24842,7 +24904,7 @@
       </c>
     </row>
     <row r="598" ht="17" customHeight="1">
-      <c r="A598" s="2" t="n">
+      <c r="A598" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B598" s="3" t="inlineStr">
@@ -24873,7 +24935,7 @@
       </c>
     </row>
     <row r="599" ht="17" customHeight="1">
-      <c r="A599" s="8" t="n">
+      <c r="A599" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B599" s="9" t="inlineStr">
@@ -24904,7 +24966,7 @@
       </c>
     </row>
     <row r="600" ht="17" customHeight="1">
-      <c r="A600" s="2" t="n">
+      <c r="A600" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B600" s="3" t="inlineStr">
@@ -24935,7 +24997,7 @@
       </c>
     </row>
     <row r="601" ht="17" customHeight="1">
-      <c r="A601" s="8" t="n">
+      <c r="A601" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B601" s="9" t="inlineStr">
@@ -24966,7 +25028,7 @@
       </c>
     </row>
     <row r="602" ht="17" customHeight="1">
-      <c r="A602" s="2" t="n">
+      <c r="A602" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B602" s="3" t="inlineStr">
@@ -24997,7 +25059,7 @@
       </c>
     </row>
     <row r="603" ht="17" customHeight="1">
-      <c r="A603" s="8" t="n">
+      <c r="A603" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B603" s="9" t="inlineStr">
@@ -25028,7 +25090,7 @@
       </c>
     </row>
     <row r="604" ht="17" customHeight="1">
-      <c r="A604" s="2" t="n">
+      <c r="A604" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B604" s="3" t="inlineStr">
@@ -25059,7 +25121,7 @@
       </c>
     </row>
     <row r="605" ht="17" customHeight="1">
-      <c r="A605" s="8" t="n">
+      <c r="A605" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B605" s="9" t="inlineStr">
@@ -25090,7 +25152,7 @@
       </c>
     </row>
     <row r="606" ht="17" customHeight="1">
-      <c r="A606" s="2" t="n">
+      <c r="A606" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B606" s="3" t="inlineStr">
@@ -25121,7 +25183,7 @@
       </c>
     </row>
     <row r="607" ht="17" customHeight="1">
-      <c r="A607" s="8" t="n">
+      <c r="A607" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B607" s="9" t="inlineStr">
@@ -25152,7 +25214,7 @@
       </c>
     </row>
     <row r="608" ht="17" customHeight="1">
-      <c r="A608" s="2" t="n">
+      <c r="A608" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B608" s="3" t="inlineStr">
@@ -25183,7 +25245,7 @@
       </c>
     </row>
     <row r="609" ht="17" customHeight="1">
-      <c r="A609" s="8" t="n">
+      <c r="A609" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B609" s="9" t="inlineStr">
@@ -25214,7 +25276,7 @@
       </c>
     </row>
     <row r="610" ht="17" customHeight="1">
-      <c r="A610" s="2" t="n">
+      <c r="A610" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B610" s="3" t="inlineStr">
@@ -25245,7 +25307,7 @@
       </c>
     </row>
     <row r="611" ht="17" customHeight="1">
-      <c r="A611" s="8" t="n">
+      <c r="A611" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B611" s="9" t="inlineStr">
@@ -25276,7 +25338,7 @@
       </c>
     </row>
     <row r="612" ht="17" customHeight="1">
-      <c r="A612" s="2" t="n">
+      <c r="A612" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B612" s="3" t="inlineStr">
@@ -25307,7 +25369,7 @@
       </c>
     </row>
     <row r="613" ht="17" customHeight="1">
-      <c r="A613" s="8" t="n">
+      <c r="A613" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B613" s="9" t="inlineStr">
@@ -25338,7 +25400,7 @@
       </c>
     </row>
     <row r="614" ht="17" customHeight="1">
-      <c r="A614" s="2" t="n">
+      <c r="A614" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B614" s="3" t="inlineStr">
@@ -25369,7 +25431,7 @@
       </c>
     </row>
     <row r="615" ht="17" customHeight="1">
-      <c r="A615" s="8" t="n">
+      <c r="A615" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B615" s="9" t="inlineStr">
@@ -25400,7 +25462,7 @@
       </c>
     </row>
     <row r="616" ht="17" customHeight="1">
-      <c r="A616" s="2" t="n">
+      <c r="A616" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B616" s="3" t="inlineStr">
@@ -25431,7 +25493,7 @@
       </c>
     </row>
     <row r="617" ht="17" customHeight="1">
-      <c r="A617" s="8" t="n">
+      <c r="A617" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B617" s="9" t="inlineStr">
@@ -25462,7 +25524,7 @@
       </c>
     </row>
     <row r="618" ht="17" customHeight="1">
-      <c r="A618" s="2" t="n">
+      <c r="A618" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B618" s="3" t="inlineStr">
@@ -25493,7 +25555,7 @@
       </c>
     </row>
     <row r="619" ht="17" customHeight="1">
-      <c r="A619" s="8" t="n">
+      <c r="A619" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B619" s="9" t="inlineStr">
@@ -25524,7 +25586,7 @@
       </c>
     </row>
     <row r="620" ht="17" customHeight="1">
-      <c r="A620" s="2" t="n">
+      <c r="A620" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B620" s="3" t="inlineStr">
@@ -25555,7 +25617,7 @@
       </c>
     </row>
     <row r="621" ht="17" customHeight="1">
-      <c r="A621" s="8" t="n">
+      <c r="A621" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B621" s="9" t="inlineStr">
@@ -25586,7 +25648,7 @@
       </c>
     </row>
     <row r="622" ht="17" customHeight="1">
-      <c r="A622" s="2" t="n">
+      <c r="A622" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B622" s="3" t="inlineStr">
@@ -25617,7 +25679,7 @@
       </c>
     </row>
     <row r="623" ht="17" customHeight="1">
-      <c r="A623" s="8" t="n">
+      <c r="A623" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B623" s="9" t="inlineStr">
@@ -25648,7 +25710,7 @@
       </c>
     </row>
     <row r="624" ht="17" customHeight="1">
-      <c r="A624" s="2" t="n">
+      <c r="A624" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B624" s="3" t="inlineStr">
@@ -25679,7 +25741,7 @@
       </c>
     </row>
     <row r="625" ht="17" customHeight="1">
-      <c r="A625" s="8" t="n">
+      <c r="A625" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B625" s="9" t="inlineStr">
@@ -25710,7 +25772,7 @@
       </c>
     </row>
     <row r="626" ht="17" customHeight="1">
-      <c r="A626" s="2" t="n">
+      <c r="A626" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B626" s="3" t="inlineStr">
@@ -25741,7 +25803,7 @@
       </c>
     </row>
     <row r="627" ht="17" customHeight="1">
-      <c r="A627" s="8" t="n">
+      <c r="A627" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B627" s="9" t="inlineStr">
@@ -25772,7 +25834,7 @@
       </c>
     </row>
     <row r="628" ht="17" customHeight="1">
-      <c r="A628" s="2" t="n">
+      <c r="A628" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B628" s="3" t="inlineStr">
@@ -25803,7 +25865,7 @@
       </c>
     </row>
     <row r="629" ht="17" customHeight="1">
-      <c r="A629" s="8" t="n">
+      <c r="A629" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B629" s="9" t="inlineStr">
@@ -25834,7 +25896,7 @@
       </c>
     </row>
     <row r="630" ht="17" customHeight="1">
-      <c r="A630" s="2" t="n">
+      <c r="A630" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B630" s="3" t="inlineStr">
@@ -25865,7 +25927,7 @@
       </c>
     </row>
     <row r="631" ht="17" customHeight="1">
-      <c r="A631" s="8" t="n">
+      <c r="A631" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B631" s="9" t="inlineStr">
@@ -25896,7 +25958,7 @@
       </c>
     </row>
     <row r="632" ht="17" customHeight="1">
-      <c r="A632" s="2" t="n">
+      <c r="A632" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B632" s="3" t="inlineStr">
@@ -25927,7 +25989,7 @@
       </c>
     </row>
     <row r="633" ht="17" customHeight="1">
-      <c r="A633" s="8" t="n">
+      <c r="A633" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B633" s="9" t="inlineStr">
@@ -25958,7 +26020,7 @@
       </c>
     </row>
     <row r="634" ht="17" customHeight="1">
-      <c r="A634" s="2" t="n">
+      <c r="A634" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B634" s="3" t="inlineStr">
@@ -25989,7 +26051,7 @@
       </c>
     </row>
     <row r="635" ht="17" customHeight="1">
-      <c r="A635" s="8" t="n">
+      <c r="A635" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B635" s="9" t="inlineStr">
@@ -26020,7 +26082,7 @@
       </c>
     </row>
     <row r="636" ht="17" customHeight="1">
-      <c r="A636" s="2" t="n">
+      <c r="A636" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B636" s="3" t="inlineStr">
@@ -26051,7 +26113,7 @@
       </c>
     </row>
     <row r="637" ht="17" customHeight="1">
-      <c r="A637" s="8" t="n">
+      <c r="A637" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B637" s="9" t="inlineStr">
@@ -26082,7 +26144,7 @@
       </c>
     </row>
     <row r="638" ht="17" customHeight="1">
-      <c r="A638" s="2" t="n">
+      <c r="A638" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B638" s="3" t="inlineStr">
@@ -26113,7 +26175,7 @@
       </c>
     </row>
     <row r="639" ht="17" customHeight="1">
-      <c r="A639" s="8" t="n">
+      <c r="A639" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B639" s="9" t="inlineStr">
@@ -26144,7 +26206,7 @@
       </c>
     </row>
     <row r="640" ht="17" customHeight="1">
-      <c r="A640" s="2" t="n">
+      <c r="A640" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B640" s="3" t="inlineStr">
@@ -26175,7 +26237,7 @@
       </c>
     </row>
     <row r="641" ht="17" customHeight="1">
-      <c r="A641" s="8" t="n">
+      <c r="A641" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B641" s="9" t="inlineStr">
@@ -26206,7 +26268,7 @@
       </c>
     </row>
     <row r="642" ht="17" customHeight="1">
-      <c r="A642" s="2" t="n">
+      <c r="A642" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B642" s="3" t="inlineStr">
@@ -26237,7 +26299,7 @@
       </c>
     </row>
     <row r="643" ht="17" customHeight="1">
-      <c r="A643" s="8" t="n">
+      <c r="A643" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B643" s="9" t="inlineStr">
@@ -26268,7 +26330,7 @@
       </c>
     </row>
     <row r="644" ht="17" customHeight="1">
-      <c r="A644" s="2" t="n">
+      <c r="A644" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B644" s="3" t="inlineStr">
@@ -26299,7 +26361,7 @@
       </c>
     </row>
     <row r="645" ht="17" customHeight="1">
-      <c r="A645" s="8" t="n">
+      <c r="A645" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B645" s="9" t="inlineStr">
@@ -26330,7 +26392,7 @@
       </c>
     </row>
     <row r="646" ht="17" customHeight="1">
-      <c r="A646" s="2" t="n">
+      <c r="A646" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B646" s="3" t="inlineStr">
@@ -26361,7 +26423,7 @@
       </c>
     </row>
     <row r="647" ht="17" customHeight="1">
-      <c r="A647" s="8" t="n">
+      <c r="A647" s="28" t="n">
         <v>46172</v>
       </c>
       <c r="B647" s="9" t="inlineStr">
@@ -26392,7 +26454,7 @@
       </c>
     </row>
     <row r="648" ht="17" customHeight="1">
-      <c r="A648" s="2" t="n">
+      <c r="A648" s="26" t="n">
         <v>46172</v>
       </c>
       <c r="B648" s="3" t="inlineStr">
